--- a/compare/output/dscale_IndustryCO2_downscaled_SSP460.xlsx
+++ b/compare/output/dscale_IndustryCO2_downscaled_SSP460.xlsx
@@ -526,19 +526,19 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>361.415807</v>
+        <v>357.764631</v>
       </c>
       <c r="F2" t="n">
-        <v>550.31928</v>
+        <v>539.2232279999999</v>
       </c>
       <c r="G2" t="n">
-        <v>816.152307</v>
+        <v>791.485159</v>
       </c>
       <c r="H2" t="n">
-        <v>1191.941744</v>
+        <v>1144.261399</v>
       </c>
       <c r="I2" t="n">
-        <v>1787.607381</v>
+        <v>1707.160921</v>
       </c>
       <c r="J2" t="n">
         <v>3707.653497</v>
@@ -602,19 +602,19 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>97.09816499999999</v>
+        <v>96.78698300000001</v>
       </c>
       <c r="F3" t="n">
-        <v>121.214616</v>
+        <v>120.288594</v>
       </c>
       <c r="G3" t="n">
-        <v>151.616385</v>
+        <v>149.598098</v>
       </c>
       <c r="H3" t="n">
-        <v>190.918837</v>
+        <v>187.026724</v>
       </c>
       <c r="I3" t="n">
-        <v>246.915222</v>
+        <v>240.2764</v>
       </c>
       <c r="J3" t="n">
         <v>419.203788</v>
@@ -678,19 +678,19 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>599.3326489999999</v>
+        <v>600.3768240000001</v>
       </c>
       <c r="F4" t="n">
-        <v>659.579187</v>
+        <v>661.908475</v>
       </c>
       <c r="G4" t="n">
-        <v>690.935882</v>
+        <v>694.7749700000001</v>
       </c>
       <c r="H4" t="n">
-        <v>716.427381</v>
+        <v>722.3457540000001</v>
       </c>
       <c r="I4" t="n">
-        <v>702.665159</v>
+        <v>711.204299</v>
       </c>
       <c r="J4" t="n">
         <v>586.63125</v>
@@ -754,19 +754,19 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>362.398012</v>
+        <v>359.611877</v>
       </c>
       <c r="F5" t="n">
-        <v>627.854679</v>
+        <v>618.899458</v>
       </c>
       <c r="G5" t="n">
-        <v>1099.904638</v>
+        <v>1078.495281</v>
       </c>
       <c r="H5" t="n">
-        <v>1759.688984</v>
+        <v>1715.814477</v>
       </c>
       <c r="I5" t="n">
-        <v>2641.678833</v>
+        <v>2564.015776</v>
       </c>
       <c r="J5" t="n">
         <v>4860.521101</v>
@@ -830,19 +830,19 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>22715.467521</v>
+        <v>22726.391086</v>
       </c>
       <c r="F6" t="n">
-        <v>31142.212032</v>
+        <v>31175.900593</v>
       </c>
       <c r="G6" t="n">
-        <v>37407.283594</v>
+        <v>37462.158106</v>
       </c>
       <c r="H6" t="n">
-        <v>42977.131896</v>
+        <v>43047.448196</v>
       </c>
       <c r="I6" t="n">
-        <v>47085.591365</v>
+        <v>47161.986898</v>
       </c>
       <c r="J6" t="n">
         <v>51453.455205</v>
@@ -906,19 +906,19 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>21880.615891</v>
+        <v>21916.929868</v>
       </c>
       <c r="F7" t="n">
-        <v>30582.903811</v>
+        <v>30698.460186</v>
       </c>
       <c r="G7" t="n">
-        <v>41489.748262</v>
+        <v>41777.014651</v>
       </c>
       <c r="H7" t="n">
-        <v>52259.92716</v>
+        <v>52876.733062</v>
       </c>
       <c r="I7" t="n">
-        <v>57528.036925</v>
+        <v>58668.061322</v>
       </c>
       <c r="J7" t="n">
         <v>42526.146793</v>
@@ -982,19 +982,19 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2786.43136</v>
+        <v>2778.647346</v>
       </c>
       <c r="F8" t="n">
-        <v>4027.308371</v>
+        <v>4003.347095</v>
       </c>
       <c r="G8" t="n">
-        <v>5681.106782</v>
+        <v>5627.038777</v>
       </c>
       <c r="H8" t="n">
-        <v>7733.651515</v>
+        <v>7626.213883</v>
       </c>
       <c r="I8" t="n">
-        <v>10236.056889</v>
+        <v>10047.897427</v>
       </c>
       <c r="J8" t="n">
         <v>16129.132264</v>
@@ -1058,19 +1058,19 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1262.587062</v>
+        <v>1263.302941</v>
       </c>
       <c r="F9" t="n">
-        <v>1358.646475</v>
+        <v>1359.719601</v>
       </c>
       <c r="G9" t="n">
-        <v>1371.483319</v>
+        <v>1372.110828</v>
       </c>
       <c r="H9" t="n">
-        <v>1371.637072</v>
+        <v>1370.930689</v>
       </c>
       <c r="I9" t="n">
-        <v>1352.400292</v>
+        <v>1349.459253</v>
       </c>
       <c r="J9" t="n">
         <v>1437.606522</v>
@@ -1134,19 +1134,19 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>790.804116</v>
+        <v>782.245233</v>
       </c>
       <c r="F10" t="n">
-        <v>1098.067769</v>
+        <v>1073.132966</v>
       </c>
       <c r="G10" t="n">
-        <v>1472.055927</v>
+        <v>1419.480948</v>
       </c>
       <c r="H10" t="n">
-        <v>2088.19998</v>
+        <v>1989.004928</v>
       </c>
       <c r="I10" t="n">
-        <v>3226.438271</v>
+        <v>3059.549951</v>
       </c>
       <c r="J10" t="n">
         <v>7220.284986</v>
@@ -1210,19 +1210,19 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>16150.116643</v>
+        <v>16141.315485</v>
       </c>
       <c r="F11" t="n">
-        <v>21597.707012</v>
+        <v>21569.441203</v>
       </c>
       <c r="G11" t="n">
-        <v>27670.832692</v>
+        <v>27606.579881</v>
       </c>
       <c r="H11" t="n">
-        <v>34357.96646</v>
+        <v>34230.714327</v>
       </c>
       <c r="I11" t="n">
-        <v>40419.420442</v>
+        <v>40193.358948</v>
       </c>
       <c r="J11" t="n">
         <v>50396.578905</v>
@@ -1286,19 +1286,19 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>476.789374</v>
+        <v>472.458505</v>
       </c>
       <c r="F12" t="n">
-        <v>725.874465</v>
+        <v>712.800516</v>
       </c>
       <c r="G12" t="n">
-        <v>1094.169145</v>
+        <v>1064.741205</v>
       </c>
       <c r="H12" t="n">
-        <v>1642.502051</v>
+        <v>1583.937594</v>
       </c>
       <c r="I12" t="n">
-        <v>2503.961309</v>
+        <v>2401.972546</v>
       </c>
       <c r="J12" t="n">
         <v>5158.552</v>
@@ -1362,19 +1362,19 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>7079.515999</v>
+        <v>7066.74182</v>
       </c>
       <c r="F13" t="n">
-        <v>9693.592003</v>
+        <v>9652.157786</v>
       </c>
       <c r="G13" t="n">
-        <v>12609.520229</v>
+        <v>12511.33126</v>
       </c>
       <c r="H13" t="n">
-        <v>16383.504711</v>
+        <v>16179.066759</v>
       </c>
       <c r="I13" t="n">
-        <v>21383.200222</v>
+        <v>21009.028571</v>
       </c>
       <c r="J13" t="n">
         <v>34023.762559</v>
@@ -1438,58 +1438,58 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>44516.000232</v>
+        <v>44517.103968</v>
       </c>
       <c r="F14" t="n">
-        <v>49136.854205</v>
+        <v>49139.157354</v>
       </c>
       <c r="G14" t="n">
-        <v>55601.320018</v>
+        <v>55605.160751</v>
       </c>
       <c r="H14" t="n">
-        <v>62965.728294</v>
+        <v>62971.46993</v>
       </c>
       <c r="I14" t="n">
-        <v>70219.163323</v>
+        <v>70227.08289000001</v>
       </c>
       <c r="J14" t="n">
-        <v>77082.000308</v>
+        <v>77092.266632</v>
       </c>
       <c r="K14" t="n">
-        <v>83793.45991799999</v>
+        <v>83806.217271</v>
       </c>
       <c r="L14" t="n">
-        <v>89356.008885</v>
+        <v>89371.228305</v>
       </c>
       <c r="M14" t="n">
-        <v>93384.887365</v>
+        <v>93402.481122</v>
       </c>
       <c r="N14" t="n">
-        <v>95985.226975</v>
+        <v>96005.126498</v>
       </c>
       <c r="O14" t="n">
-        <v>97642.021811</v>
+        <v>97664.23514999999</v>
       </c>
       <c r="P14" t="n">
-        <v>98305.20454799999</v>
+        <v>98329.658918</v>
       </c>
       <c r="Q14" t="n">
-        <v>98286.91676599999</v>
+        <v>98313.551139</v>
       </c>
       <c r="R14" t="n">
-        <v>98007.531006</v>
+        <v>98036.369957</v>
       </c>
       <c r="S14" t="n">
-        <v>97663.98061100001</v>
+        <v>97695.110571</v>
       </c>
       <c r="T14" t="n">
-        <v>97265.063393</v>
+        <v>97298.582367</v>
       </c>
       <c r="U14" t="n">
-        <v>96689.104727</v>
+        <v>96725.08173599999</v>
       </c>
       <c r="V14" t="n">
-        <v>95831.953611</v>
+        <v>95870.43773999999</v>
       </c>
     </row>
     <row r="15">
@@ -1514,58 +1514,58 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>58914.263894</v>
+        <v>58913.790276</v>
       </c>
       <c r="F15" t="n">
-        <v>71871.582773</v>
+        <v>71870.811865</v>
       </c>
       <c r="G15" t="n">
-        <v>85379.062668</v>
+        <v>85378.04832</v>
       </c>
       <c r="H15" t="n">
-        <v>98679.21466</v>
+        <v>98677.87475</v>
       </c>
       <c r="I15" t="n">
-        <v>110488.377123</v>
+        <v>110486.530826</v>
       </c>
       <c r="J15" t="n">
-        <v>120827.534494</v>
+        <v>120824.959706</v>
       </c>
       <c r="K15" t="n">
-        <v>130809.543297</v>
+        <v>130806.056319</v>
       </c>
       <c r="L15" t="n">
-        <v>139592.499679</v>
+        <v>139588.014719</v>
       </c>
       <c r="M15" t="n">
-        <v>146684.286188</v>
+        <v>146678.787215</v>
       </c>
       <c r="N15" t="n">
-        <v>151935.719763</v>
+        <v>151929.217835</v>
       </c>
       <c r="O15" t="n">
-        <v>155765.428382</v>
+        <v>155757.949638</v>
       </c>
       <c r="P15" t="n">
-        <v>157878.392921</v>
+        <v>157870.0125</v>
       </c>
       <c r="Q15" t="n">
-        <v>158647.295655</v>
+        <v>158638.089244</v>
       </c>
       <c r="R15" t="n">
-        <v>158696.714899</v>
+        <v>158686.713961</v>
       </c>
       <c r="S15" t="n">
-        <v>158324.91186</v>
+        <v>158314.102721</v>
       </c>
       <c r="T15" t="n">
-        <v>157511.156369</v>
+        <v>157499.495134</v>
       </c>
       <c r="U15" t="n">
-        <v>156043.755034</v>
+        <v>156031.197262</v>
       </c>
       <c r="V15" t="n">
-        <v>153822.154939</v>
+        <v>153808.66762</v>
       </c>
     </row>
     <row r="16">
@@ -1590,58 +1590,58 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>10608.846436</v>
+        <v>10609.022044</v>
       </c>
       <c r="F16" t="n">
-        <v>10320.548462</v>
+        <v>10320.760965</v>
       </c>
       <c r="G16" t="n">
-        <v>9970.675509000001</v>
+        <v>9970.779325</v>
       </c>
       <c r="H16" t="n">
-        <v>9981.89867</v>
+        <v>9981.818375999999</v>
       </c>
       <c r="I16" t="n">
-        <v>10224.476313</v>
+        <v>10224.173659</v>
       </c>
       <c r="J16" t="n">
-        <v>10636.056902</v>
+        <v>10635.514244</v>
       </c>
       <c r="K16" t="n">
-        <v>11203.648872</v>
+        <v>11202.853539</v>
       </c>
       <c r="L16" t="n">
-        <v>11758.933469</v>
+        <v>11757.88274</v>
       </c>
       <c r="M16" t="n">
-        <v>12215.463249</v>
+        <v>12214.166939</v>
       </c>
       <c r="N16" t="n">
-        <v>12533.875004</v>
+        <v>12532.345262</v>
       </c>
       <c r="O16" t="n">
-        <v>12728.774599</v>
+        <v>12727.012126</v>
       </c>
       <c r="P16" t="n">
-        <v>12773.747891</v>
+        <v>12771.746183</v>
       </c>
       <c r="Q16" t="n">
-        <v>12711.943639</v>
+        <v>12709.690409</v>
       </c>
       <c r="R16" t="n">
-        <v>12609.743276</v>
+        <v>12607.224157</v>
       </c>
       <c r="S16" t="n">
-        <v>12503.683768</v>
+        <v>12500.888364</v>
       </c>
       <c r="T16" t="n">
-        <v>12398.159154</v>
+        <v>12395.084499</v>
       </c>
       <c r="U16" t="n">
-        <v>12279.623283</v>
+        <v>12276.27529</v>
       </c>
       <c r="V16" t="n">
-        <v>12129.712866</v>
+        <v>12126.098064</v>
       </c>
     </row>
     <row r="17">
@@ -1666,58 +1666,58 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>10367.807236</v>
+        <v>10367.05815</v>
       </c>
       <c r="F17" t="n">
-        <v>11408.913979</v>
+        <v>11407.249127</v>
       </c>
       <c r="G17" t="n">
-        <v>12443.897463</v>
+        <v>12441.100793</v>
       </c>
       <c r="H17" t="n">
-        <v>13414.07035</v>
+        <v>13409.958775</v>
       </c>
       <c r="I17" t="n">
-        <v>14136.215028</v>
+        <v>14130.707697</v>
       </c>
       <c r="J17" t="n">
-        <v>14539.931283</v>
+        <v>14533.008336</v>
       </c>
       <c r="K17" t="n">
-        <v>14829.503751</v>
+        <v>14821.118024</v>
       </c>
       <c r="L17" t="n">
-        <v>15019.079365</v>
+        <v>15009.247115</v>
       </c>
       <c r="M17" t="n">
-        <v>15171.480309</v>
+        <v>15160.263902</v>
       </c>
       <c r="N17" t="n">
-        <v>15293.753893</v>
+        <v>15281.251863</v>
       </c>
       <c r="O17" t="n">
-        <v>15410.829976</v>
+        <v>15397.113264</v>
       </c>
       <c r="P17" t="n">
-        <v>15448.950271</v>
+        <v>15434.129953</v>
       </c>
       <c r="Q17" t="n">
-        <v>15412.740395</v>
+        <v>15396.889683</v>
       </c>
       <c r="R17" t="n">
-        <v>15369.666452</v>
+        <v>15352.781291</v>
       </c>
       <c r="S17" t="n">
-        <v>15368.056075</v>
+        <v>15350.084534</v>
       </c>
       <c r="T17" t="n">
-        <v>15430.551974</v>
+        <v>15411.439174</v>
       </c>
       <c r="U17" t="n">
-        <v>15553.286706</v>
+        <v>15532.992299</v>
       </c>
       <c r="V17" t="n">
-        <v>15701.174976</v>
+        <v>15679.664962</v>
       </c>
     </row>
     <row r="18">
@@ -1742,58 +1742,58 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>8241.564956</v>
+        <v>8241.508315999999</v>
       </c>
       <c r="F18" t="n">
-        <v>9814.818255</v>
+        <v>9814.738362</v>
       </c>
       <c r="G18" t="n">
-        <v>11038.510839</v>
+        <v>11038.377308</v>
       </c>
       <c r="H18" t="n">
-        <v>12216.805577</v>
+        <v>12216.59572</v>
       </c>
       <c r="I18" t="n">
-        <v>13421.64197</v>
+        <v>13421.378685</v>
       </c>
       <c r="J18" t="n">
-        <v>14852.307754</v>
+        <v>14852.081823</v>
       </c>
       <c r="K18" t="n">
-        <v>16506.807137</v>
+        <v>16506.717823</v>
       </c>
       <c r="L18" t="n">
-        <v>18155.06487</v>
+        <v>18155.213387</v>
       </c>
       <c r="M18" t="n">
-        <v>19445.782839</v>
+        <v>19446.200772</v>
       </c>
       <c r="N18" t="n">
-        <v>20162.003229</v>
+        <v>20162.637406</v>
       </c>
       <c r="O18" t="n">
-        <v>20311.63691</v>
+        <v>20312.3815</v>
       </c>
       <c r="P18" t="n">
-        <v>19977.695931</v>
+        <v>19978.444007</v>
       </c>
       <c r="Q18" t="n">
-        <v>19369.220137</v>
+        <v>19369.896116</v>
       </c>
       <c r="R18" t="n">
-        <v>18685.143122</v>
+        <v>18685.709387</v>
       </c>
       <c r="S18" t="n">
-        <v>18028.734779</v>
+        <v>18029.180904</v>
       </c>
       <c r="T18" t="n">
-        <v>17428.020058</v>
+        <v>17428.349776</v>
       </c>
       <c r="U18" t="n">
-        <v>16862.696108</v>
+        <v>16862.919271</v>
       </c>
       <c r="V18" t="n">
-        <v>16301.333547</v>
+        <v>16301.461553</v>
       </c>
     </row>
     <row r="19">
@@ -1818,19 +1818,19 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>20034.017592</v>
+        <v>20039.682951</v>
       </c>
       <c r="F19" t="n">
-        <v>27489.765482</v>
+        <v>27508.267513</v>
       </c>
       <c r="G19" t="n">
-        <v>34986.907002</v>
+        <v>35030.779584</v>
       </c>
       <c r="H19" t="n">
-        <v>41825.828144</v>
+        <v>41921.869184</v>
       </c>
       <c r="I19" t="n">
-        <v>46600.920991</v>
+        <v>46831.340239</v>
       </c>
       <c r="J19" t="n">
         <v>33936.227851</v>
@@ -1894,19 +1894,19 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1204.315927</v>
+        <v>1203.906818</v>
       </c>
       <c r="F20" t="n">
-        <v>1605.3541</v>
+        <v>1604.142698</v>
       </c>
       <c r="G20" t="n">
-        <v>2071.442921</v>
+        <v>2068.732223</v>
       </c>
       <c r="H20" t="n">
-        <v>2463.073458</v>
+        <v>2457.430554</v>
       </c>
       <c r="I20" t="n">
-        <v>2738.272641</v>
+        <v>2725.226792</v>
       </c>
       <c r="J20" t="n">
         <v>3935.527322</v>
@@ -1970,19 +1970,19 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>138.743048</v>
+        <v>138.499224</v>
       </c>
       <c r="F21" t="n">
-        <v>155.138071</v>
+        <v>154.460837</v>
       </c>
       <c r="G21" t="n">
-        <v>171.16138</v>
+        <v>169.71533</v>
       </c>
       <c r="H21" t="n">
-        <v>193.626787</v>
+        <v>190.663451</v>
       </c>
       <c r="I21" t="n">
-        <v>234.622397</v>
+        <v>227.78514</v>
       </c>
       <c r="J21" t="n">
         <v>796.066634</v>
@@ -2046,19 +2046,19 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3559.129332</v>
+        <v>3558.351429</v>
       </c>
       <c r="F22" t="n">
-        <v>4966.901853</v>
+        <v>4964.47301</v>
       </c>
       <c r="G22" t="n">
-        <v>6382.422241</v>
+        <v>6376.526159</v>
       </c>
       <c r="H22" t="n">
-        <v>7692.820657</v>
+        <v>7679.324515</v>
       </c>
       <c r="I22" t="n">
-        <v>8817.864265</v>
+        <v>8783.797957999999</v>
       </c>
       <c r="J22" t="n">
         <v>12792.991516</v>
@@ -2122,19 +2122,19 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2776.030602</v>
+        <v>2776.107086</v>
       </c>
       <c r="F23" t="n">
-        <v>4121.392015</v>
+        <v>4121.783521</v>
       </c>
       <c r="G23" t="n">
-        <v>5756.065168</v>
+        <v>5757.281355</v>
       </c>
       <c r="H23" t="n">
-        <v>7642.327661</v>
+        <v>7645.715318</v>
       </c>
       <c r="I23" t="n">
-        <v>9568.848470000001</v>
+        <v>9578.827334</v>
       </c>
       <c r="J23" t="n">
         <v>10933.739876</v>
@@ -2198,19 +2198,19 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>925.6145780000001</v>
+        <v>925.310335</v>
       </c>
       <c r="F24" t="n">
-        <v>1203.803197</v>
+        <v>1202.867156</v>
       </c>
       <c r="G24" t="n">
-        <v>1506.445467</v>
+        <v>1504.24483</v>
       </c>
       <c r="H24" t="n">
-        <v>1784.626266</v>
+        <v>1779.794323</v>
       </c>
       <c r="I24" t="n">
-        <v>2029.018874</v>
+        <v>2017.323763</v>
       </c>
       <c r="J24" t="n">
         <v>3187.736899</v>
@@ -2274,19 +2274,19 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>338.762269</v>
+        <v>338.622932</v>
       </c>
       <c r="F25" t="n">
-        <v>395.504602</v>
+        <v>395.089641</v>
       </c>
       <c r="G25" t="n">
-        <v>451.019335</v>
+        <v>450.07957</v>
       </c>
       <c r="H25" t="n">
-        <v>507.872359</v>
+        <v>505.875107</v>
       </c>
       <c r="I25" t="n">
-        <v>566.926205</v>
+        <v>562.215688</v>
       </c>
       <c r="J25" t="n">
         <v>988.312789</v>
@@ -2350,19 +2350,19 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4833.660836</v>
+        <v>4828.863678</v>
       </c>
       <c r="F26" t="n">
-        <v>6472.3963</v>
+        <v>6456.860848</v>
       </c>
       <c r="G26" t="n">
-        <v>7973.374025</v>
+        <v>7935.854654</v>
       </c>
       <c r="H26" t="n">
-        <v>9565.868922</v>
+        <v>9481.065408</v>
       </c>
       <c r="I26" t="n">
-        <v>11605.719816</v>
+        <v>11393.863827</v>
       </c>
       <c r="J26" t="n">
         <v>31108.502092</v>
@@ -2426,19 +2426,19 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3677.755583</v>
+        <v>3676.916408</v>
       </c>
       <c r="F27" t="n">
-        <v>5013.164473</v>
+        <v>5010.331633</v>
       </c>
       <c r="G27" t="n">
-        <v>6201.150122</v>
+        <v>6193.813799</v>
       </c>
       <c r="H27" t="n">
-        <v>7366.93362</v>
+        <v>7349.328587</v>
       </c>
       <c r="I27" t="n">
-        <v>8574.887167999999</v>
+        <v>8528.537682</v>
       </c>
       <c r="J27" t="n">
         <v>13954.51986</v>
@@ -2502,19 +2502,19 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3245.374068</v>
+        <v>3247.142975</v>
       </c>
       <c r="F28" t="n">
-        <v>3937.070978</v>
+        <v>3942.214215</v>
       </c>
       <c r="G28" t="n">
-        <v>5142.8589</v>
+        <v>5155.819057</v>
       </c>
       <c r="H28" t="n">
-        <v>6614.097901</v>
+        <v>6646.009328</v>
       </c>
       <c r="I28" t="n">
-        <v>7963.412657</v>
+        <v>8051.575061</v>
       </c>
       <c r="J28" t="n">
         <v>1704.032756</v>
@@ -2578,19 +2578,19 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1694.794303</v>
+        <v>1694.417546</v>
       </c>
       <c r="F29" t="n">
-        <v>2216.804491</v>
+        <v>2215.586629</v>
       </c>
       <c r="G29" t="n">
-        <v>2956.918583</v>
+        <v>2953.899615</v>
       </c>
       <c r="H29" t="n">
-        <v>3785.809379</v>
+        <v>3778.807355</v>
       </c>
       <c r="I29" t="n">
-        <v>4601.177421</v>
+        <v>4582.960017</v>
       </c>
       <c r="J29" t="n">
         <v>7390.165935</v>
@@ -2654,19 +2654,19 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1912.115849</v>
+        <v>1911.332371</v>
       </c>
       <c r="F30" t="n">
-        <v>2029.98061</v>
+        <v>2027.716655</v>
       </c>
       <c r="G30" t="n">
-        <v>2207.267157</v>
+        <v>2202.127034</v>
       </c>
       <c r="H30" t="n">
-        <v>2539.30608</v>
+        <v>2527.728329</v>
       </c>
       <c r="I30" t="n">
-        <v>3041.753784</v>
+        <v>3011.339107</v>
       </c>
       <c r="J30" t="n">
         <v>7079.239678</v>
@@ -2730,19 +2730,19 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>67.515872</v>
+        <v>67.191597</v>
       </c>
       <c r="F31" t="n">
-        <v>89.190375</v>
+        <v>88.18905100000001</v>
       </c>
       <c r="G31" t="n">
-        <v>118.120494</v>
+        <v>115.712178</v>
       </c>
       <c r="H31" t="n">
-        <v>161.696173</v>
+        <v>156.147861</v>
       </c>
       <c r="I31" t="n">
-        <v>248.240703</v>
+        <v>233.879893</v>
       </c>
       <c r="J31" t="n">
         <v>1877.3556</v>
@@ -2806,19 +2806,19 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5427.023319</v>
+        <v>5426.764686</v>
       </c>
       <c r="F32" t="n">
-        <v>6267.978641</v>
+        <v>6267.068157</v>
       </c>
       <c r="G32" t="n">
-        <v>7358.212988</v>
+        <v>7356.078407</v>
       </c>
       <c r="H32" t="n">
-        <v>8623.621404</v>
+        <v>8619.141228</v>
       </c>
       <c r="I32" t="n">
-        <v>9859.644851999999</v>
+        <v>9849.150115</v>
       </c>
       <c r="J32" t="n">
         <v>12252.866992</v>
@@ -2882,19 +2882,19 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6226.158036</v>
+        <v>6225.364726</v>
       </c>
       <c r="F33" t="n">
-        <v>7838.683947</v>
+        <v>7836.184064</v>
       </c>
       <c r="G33" t="n">
-        <v>9992.694571</v>
+        <v>9986.863944000001</v>
       </c>
       <c r="H33" t="n">
-        <v>12321.36135</v>
+        <v>12308.70562</v>
       </c>
       <c r="I33" t="n">
-        <v>14430.253847</v>
+        <v>14399.190379</v>
       </c>
       <c r="J33" t="n">
         <v>19620.932968</v>
@@ -2958,19 +2958,19 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1255.524876</v>
+        <v>1252.27426</v>
       </c>
       <c r="F34" t="n">
-        <v>2843.613441</v>
+        <v>2828.258748</v>
       </c>
       <c r="G34" t="n">
-        <v>6301.807712</v>
+        <v>6245.805154</v>
       </c>
       <c r="H34" t="n">
-        <v>11714.332589</v>
+        <v>11542.463797</v>
       </c>
       <c r="I34" t="n">
-        <v>19455.358746</v>
+        <v>18919.709092</v>
       </c>
       <c r="J34" t="n">
         <v>91981.23452899999</v>
@@ -3034,19 +3034,19 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5118.698183</v>
+        <v>5119.937254</v>
       </c>
       <c r="F35" t="n">
-        <v>7998.880456</v>
+        <v>8003.772894</v>
       </c>
       <c r="G35" t="n">
-        <v>12366.675912</v>
+        <v>12382.355518</v>
       </c>
       <c r="H35" t="n">
-        <v>16955.676156</v>
+        <v>16999.353043</v>
       </c>
       <c r="I35" t="n">
-        <v>20170.498117</v>
+        <v>20295.313979</v>
       </c>
       <c r="J35" t="n">
         <v>8649.487002</v>
@@ -3110,19 +3110,19 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>230.671657</v>
+        <v>230.602591</v>
       </c>
       <c r="F36" t="n">
-        <v>295.308942</v>
+        <v>295.101355</v>
       </c>
       <c r="G36" t="n">
-        <v>338.662801</v>
+        <v>338.204875</v>
       </c>
       <c r="H36" t="n">
-        <v>362.192174</v>
+        <v>361.255828</v>
       </c>
       <c r="I36" t="n">
-        <v>372.547298</v>
+        <v>370.386715</v>
       </c>
       <c r="J36" t="n">
         <v>589.217272</v>
@@ -3186,19 +3186,19 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>8348.455303000001</v>
+        <v>8351.080687</v>
       </c>
       <c r="F37" t="n">
-        <v>9256.70751</v>
+        <v>9263.772136</v>
       </c>
       <c r="G37" t="n">
-        <v>10328.554805</v>
+        <v>10344.219884</v>
       </c>
       <c r="H37" t="n">
-        <v>11328.097426</v>
+        <v>11362.115962</v>
       </c>
       <c r="I37" t="n">
-        <v>11764.47728</v>
+        <v>11848.529788</v>
       </c>
       <c r="J37" t="n">
         <v>3534.491008</v>
@@ -3262,19 +3262,19 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6678.854343</v>
+        <v>6678.196292</v>
       </c>
       <c r="F38" t="n">
-        <v>8791.606921000001</v>
+        <v>8789.514089</v>
       </c>
       <c r="G38" t="n">
-        <v>11182.422246</v>
+        <v>11177.530939</v>
       </c>
       <c r="H38" t="n">
-        <v>13786.055839</v>
+        <v>13775.433899</v>
       </c>
       <c r="I38" t="n">
-        <v>16355.663494</v>
+        <v>16329.553995</v>
       </c>
       <c r="J38" t="n">
         <v>21886.442694</v>
@@ -3338,19 +3338,19 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1345.024379</v>
+        <v>1344.686151</v>
       </c>
       <c r="F39" t="n">
-        <v>1562.010361</v>
+        <v>1560.994261</v>
       </c>
       <c r="G39" t="n">
-        <v>1876.281789</v>
+        <v>1873.90811</v>
       </c>
       <c r="H39" t="n">
-        <v>2244.680705</v>
+        <v>2239.391316</v>
       </c>
       <c r="I39" t="n">
-        <v>2621.12785</v>
+        <v>2607.779177</v>
       </c>
       <c r="J39" t="n">
         <v>4403.526313</v>
@@ -3414,19 +3414,19 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>105.465538</v>
+        <v>105.346201</v>
       </c>
       <c r="F40" t="n">
-        <v>135.451786</v>
+        <v>135.080652</v>
       </c>
       <c r="G40" t="n">
-        <v>173.962198</v>
+        <v>173.05692</v>
       </c>
       <c r="H40" t="n">
-        <v>215.64287</v>
+        <v>213.572726</v>
       </c>
       <c r="I40" t="n">
-        <v>268.708449</v>
+        <v>263.389998</v>
       </c>
       <c r="J40" t="n">
         <v>881.9910190000001</v>
@@ -3490,19 +3490,19 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>149.056944</v>
+        <v>148.803824</v>
       </c>
       <c r="F41" t="n">
-        <v>215.173278</v>
+        <v>214.314601</v>
       </c>
       <c r="G41" t="n">
-        <v>290.442438</v>
+        <v>288.265267</v>
       </c>
       <c r="H41" t="n">
-        <v>375.801048</v>
+        <v>370.679227</v>
       </c>
       <c r="I41" t="n">
-        <v>491.671401</v>
+        <v>478.301145</v>
       </c>
       <c r="J41" t="n">
         <v>2042.065372</v>
@@ -3566,19 +3566,19 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>7907.108837</v>
+        <v>7909.592296</v>
       </c>
       <c r="F42" t="n">
-        <v>9690.195328</v>
+        <v>9697.614973</v>
       </c>
       <c r="G42" t="n">
-        <v>11885.799053</v>
+        <v>11903.964807</v>
       </c>
       <c r="H42" t="n">
-        <v>13952.675852</v>
+        <v>13994.994888</v>
       </c>
       <c r="I42" t="n">
-        <v>15201.11219</v>
+        <v>15310.932008</v>
       </c>
       <c r="J42" t="n">
         <v>4611.676132</v>
@@ -3642,19 +3642,19 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>527.181747</v>
+        <v>527.144083</v>
       </c>
       <c r="F43" t="n">
-        <v>902.9110470000001</v>
+        <v>902.804917</v>
       </c>
       <c r="G43" t="n">
-        <v>1473.380059</v>
+        <v>1473.231699</v>
       </c>
       <c r="H43" t="n">
-        <v>2187.335341</v>
+        <v>2187.370565</v>
       </c>
       <c r="I43" t="n">
-        <v>2913.680755</v>
+        <v>2914.771444</v>
       </c>
       <c r="J43" t="n">
         <v>3449.543837</v>
@@ -3718,19 +3718,19 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1353.283267</v>
+        <v>1351.970832</v>
       </c>
       <c r="F44" t="n">
-        <v>1870.684574</v>
+        <v>1866.312601</v>
       </c>
       <c r="G44" t="n">
-        <v>2582.549257</v>
+        <v>2571.145997</v>
       </c>
       <c r="H44" t="n">
-        <v>3485.692927</v>
+        <v>3457.527645</v>
       </c>
       <c r="I44" t="n">
-        <v>4636.81695</v>
+        <v>4559.279231</v>
       </c>
       <c r="J44" t="n">
         <v>14620.281437</v>
@@ -3794,19 +3794,19 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1424.5593</v>
+        <v>1424.557526</v>
       </c>
       <c r="F45" t="n">
-        <v>1965.358493</v>
+        <v>1965.380727</v>
       </c>
       <c r="G45" t="n">
-        <v>2613.35464</v>
+        <v>2613.546034</v>
       </c>
       <c r="H45" t="n">
-        <v>3258.313699</v>
+        <v>3259.063589</v>
       </c>
       <c r="I45" t="n">
-        <v>3792.906613</v>
+        <v>3795.444073</v>
       </c>
       <c r="J45" t="n">
         <v>3994.864411</v>
@@ -3870,19 +3870,19 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>649.848598</v>
+        <v>648.979789</v>
       </c>
       <c r="F46" t="n">
-        <v>886.4971829999999</v>
+        <v>883.604169</v>
       </c>
       <c r="G46" t="n">
-        <v>1254.81028</v>
+        <v>1247.033725</v>
       </c>
       <c r="H46" t="n">
-        <v>1787.993151</v>
+        <v>1767.823217</v>
       </c>
       <c r="I46" t="n">
-        <v>2685.292544</v>
+        <v>2624.793785</v>
       </c>
       <c r="J46" t="n">
         <v>11506.286666</v>
@@ -3946,19 +3946,19 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>98467.094845</v>
+        <v>98471.081166</v>
       </c>
       <c r="F47" t="n">
-        <v>147855.089159</v>
+        <v>147873.717955</v>
       </c>
       <c r="G47" t="n">
-        <v>204732.799544</v>
+        <v>204794.43882</v>
       </c>
       <c r="H47" t="n">
-        <v>266077.146197</v>
+        <v>266256.415469</v>
       </c>
       <c r="I47" t="n">
-        <v>324476.377511</v>
+        <v>325029.223732</v>
       </c>
       <c r="J47" t="n">
         <v>320751.632611</v>
@@ -4022,19 +4022,19 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6312.255891</v>
+        <v>6312.986898</v>
       </c>
       <c r="F48" t="n">
-        <v>8165.453685</v>
+        <v>8167.730353</v>
       </c>
       <c r="G48" t="n">
-        <v>10500.485025</v>
+        <v>10506.503152</v>
       </c>
       <c r="H48" t="n">
-        <v>12849.61709</v>
+        <v>12864.614936</v>
       </c>
       <c r="I48" t="n">
-        <v>14627.399899</v>
+        <v>14667.965697</v>
       </c>
       <c r="J48" t="n">
         <v>11843.844941</v>
@@ -4098,19 +4098,19 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>482.377937</v>
+        <v>481.891207</v>
       </c>
       <c r="F49" t="n">
-        <v>668.8828999999999</v>
+        <v>667.277752</v>
       </c>
       <c r="G49" t="n">
-        <v>891.787686</v>
+        <v>887.744198</v>
       </c>
       <c r="H49" t="n">
-        <v>1130.318978</v>
+        <v>1120.854206</v>
       </c>
       <c r="I49" t="n">
-        <v>1401.715167</v>
+        <v>1377.172137</v>
       </c>
       <c r="J49" t="n">
         <v>4287.208523</v>
@@ -4174,19 +4174,19 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>40.993394</v>
+        <v>40.980391</v>
       </c>
       <c r="F50" t="n">
-        <v>52.86413</v>
+        <v>52.824103</v>
       </c>
       <c r="G50" t="n">
-        <v>63.952144</v>
+        <v>63.859588</v>
       </c>
       <c r="H50" t="n">
-        <v>73.080251</v>
+        <v>72.880455</v>
       </c>
       <c r="I50" t="n">
-        <v>80.074028</v>
+        <v>79.589225</v>
       </c>
       <c r="J50" t="n">
         <v>135.524738</v>
@@ -4250,19 +4250,19 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1411.184866</v>
+        <v>1410.104822</v>
       </c>
       <c r="F51" t="n">
-        <v>1752.111605</v>
+        <v>1748.769908</v>
       </c>
       <c r="G51" t="n">
-        <v>2211.64803</v>
+        <v>2203.459791</v>
       </c>
       <c r="H51" t="n">
-        <v>2748.554598</v>
+        <v>2729.445816</v>
       </c>
       <c r="I51" t="n">
-        <v>3403.409236</v>
+        <v>3353.139536</v>
       </c>
       <c r="J51" t="n">
         <v>9584.619545</v>
@@ -4326,19 +4326,19 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1045.381216</v>
+        <v>1045.341306</v>
       </c>
       <c r="F52" t="n">
-        <v>1166.691484</v>
+        <v>1166.539595</v>
       </c>
       <c r="G52" t="n">
-        <v>1326.771603</v>
+        <v>1326.405357</v>
       </c>
       <c r="H52" t="n">
-        <v>1509.689979</v>
+        <v>1508.904279</v>
       </c>
       <c r="I52" t="n">
-        <v>1679.260302</v>
+        <v>1677.374169</v>
       </c>
       <c r="J52" t="n">
         <v>2057.45607</v>
@@ -4478,58 +4478,58 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>82539.710221</v>
+        <v>82540.110765</v>
       </c>
       <c r="F54" t="n">
-        <v>89318.145813</v>
+        <v>89319.04657000001</v>
       </c>
       <c r="G54" t="n">
-        <v>101075.744708</v>
+        <v>101077.279099</v>
       </c>
       <c r="H54" t="n">
-        <v>107837.130069</v>
+        <v>107839.302607</v>
       </c>
       <c r="I54" t="n">
-        <v>115287.685539</v>
+        <v>115290.572673</v>
       </c>
       <c r="J54" t="n">
-        <v>125442.892649</v>
+        <v>125446.638451</v>
       </c>
       <c r="K54" t="n">
-        <v>139213.195959</v>
+        <v>139218.013412</v>
       </c>
       <c r="L54" t="n">
-        <v>154393.861758</v>
+        <v>154399.9317</v>
       </c>
       <c r="M54" t="n">
-        <v>165612.345778</v>
+        <v>165619.647074</v>
       </c>
       <c r="N54" t="n">
-        <v>171072.401006</v>
+        <v>171080.786233</v>
       </c>
       <c r="O54" t="n">
-        <v>174140.387982</v>
+        <v>174149.848858</v>
       </c>
       <c r="P54" t="n">
-        <v>174847.563908</v>
+        <v>174858.081184</v>
       </c>
       <c r="Q54" t="n">
-        <v>174494.483686</v>
+        <v>174506.106225</v>
       </c>
       <c r="R54" t="n">
-        <v>173727.991802</v>
+        <v>173740.816598</v>
       </c>
       <c r="S54" t="n">
-        <v>172651.870141</v>
+        <v>172666.023965</v>
       </c>
       <c r="T54" t="n">
-        <v>171175.359485</v>
+        <v>171191.021794</v>
       </c>
       <c r="U54" t="n">
-        <v>169033.850188</v>
+        <v>169051.290334</v>
       </c>
       <c r="V54" t="n">
-        <v>165914.055824</v>
+        <v>165933.511931</v>
       </c>
     </row>
     <row r="55">
@@ -4554,58 +4554,58 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>10950.373277</v>
+        <v>10949.972732</v>
       </c>
       <c r="F55" t="n">
-        <v>11032.910563</v>
+        <v>11032.009807</v>
       </c>
       <c r="G55" t="n">
-        <v>11801.2671</v>
+        <v>11799.732708</v>
       </c>
       <c r="H55" t="n">
-        <v>12064.302672</v>
+        <v>12062.130135</v>
       </c>
       <c r="I55" t="n">
-        <v>12492.790323</v>
+        <v>12489.903189</v>
       </c>
       <c r="J55" t="n">
-        <v>13273.840031</v>
+        <v>13270.094228</v>
       </c>
       <c r="K55" t="n">
-        <v>14470.700714</v>
+        <v>14465.88326</v>
       </c>
       <c r="L55" t="n">
-        <v>15830.371157</v>
+        <v>15824.301214</v>
       </c>
       <c r="M55" t="n">
-        <v>16797.432519</v>
+        <v>16790.131224</v>
       </c>
       <c r="N55" t="n">
-        <v>17210.336567</v>
+        <v>17201.95134</v>
       </c>
       <c r="O55" t="n">
-        <v>17437.379313</v>
+        <v>17427.918437</v>
       </c>
       <c r="P55" t="n">
-        <v>17496.34018</v>
+        <v>17485.822903</v>
       </c>
       <c r="Q55" t="n">
-        <v>17522.15724</v>
+        <v>17510.534701</v>
       </c>
       <c r="R55" t="n">
-        <v>17579.641127</v>
+        <v>17566.816331</v>
       </c>
       <c r="S55" t="n">
-        <v>17673.124657</v>
+        <v>17658.970832</v>
       </c>
       <c r="T55" t="n">
-        <v>17798.057189</v>
+        <v>17782.39488</v>
       </c>
       <c r="U55" t="n">
-        <v>17933.73458</v>
+        <v>17916.294433</v>
       </c>
       <c r="V55" t="n">
-        <v>18039.322903</v>
+        <v>18019.866796</v>
       </c>
     </row>
     <row r="56">
@@ -4782,19 +4782,19 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>85.95780499999999</v>
+        <v>85.35674</v>
       </c>
       <c r="F58" t="n">
-        <v>119.801794</v>
+        <v>118.165349</v>
       </c>
       <c r="G58" t="n">
-        <v>185.735869</v>
+        <v>182.131633</v>
       </c>
       <c r="H58" t="n">
-        <v>279.869141</v>
+        <v>273.249924</v>
       </c>
       <c r="I58" t="n">
-        <v>447.262562</v>
+        <v>436.653655</v>
       </c>
       <c r="J58" t="n">
         <v>962.992702</v>
@@ -4858,19 +4858,19 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>23.033517</v>
+        <v>22.667024</v>
       </c>
       <c r="F59" t="n">
-        <v>39.281801</v>
+        <v>38.238614</v>
       </c>
       <c r="G59" t="n">
-        <v>72.909205</v>
+        <v>70.503387</v>
       </c>
       <c r="H59" t="n">
-        <v>128.774766</v>
+        <v>124.197283</v>
       </c>
       <c r="I59" t="n">
-        <v>240.549112</v>
+        <v>233.008587</v>
       </c>
       <c r="J59" t="n">
         <v>612.428418</v>
@@ -4934,19 +4934,19 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>127.943595</v>
+        <v>127.637162</v>
       </c>
       <c r="F60" t="n">
-        <v>134.679033</v>
+        <v>133.924003</v>
       </c>
       <c r="G60" t="n">
-        <v>158.224219</v>
+        <v>156.725713</v>
       </c>
       <c r="H60" t="n">
-        <v>188.512736</v>
+        <v>185.98106</v>
       </c>
       <c r="I60" t="n">
-        <v>243.225664</v>
+        <v>239.427253</v>
       </c>
       <c r="J60" t="n">
         <v>413.936798</v>
@@ -5010,19 +5010,19 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2259.420968</v>
+        <v>2255.548154</v>
       </c>
       <c r="F61" t="n">
-        <v>2810.793833</v>
+        <v>2800.694255</v>
       </c>
       <c r="G61" t="n">
-        <v>3651.894317</v>
+        <v>3631.173608</v>
       </c>
       <c r="H61" t="n">
-        <v>4468.573021</v>
+        <v>4432.599391</v>
       </c>
       <c r="I61" t="n">
-        <v>5548.931336</v>
+        <v>5493.169414</v>
       </c>
       <c r="J61" t="n">
         <v>8434.624381</v>
@@ -5086,19 +5086,19 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>10611.789118</v>
+        <v>10608.838635</v>
       </c>
       <c r="F62" t="n">
-        <v>13585.479762</v>
+        <v>13583.494381</v>
       </c>
       <c r="G62" t="n">
-        <v>17272.65095</v>
+        <v>17282.431941</v>
       </c>
       <c r="H62" t="n">
-        <v>19261.531696</v>
+        <v>19296.853979</v>
       </c>
       <c r="I62" t="n">
-        <v>19458.933191</v>
+        <v>19528.65683</v>
       </c>
       <c r="J62" t="n">
         <v>16799.699709</v>
@@ -5162,19 +5162,19 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6726.890233</v>
+        <v>6721.421255</v>
       </c>
       <c r="F63" t="n">
-        <v>8488.380150000001</v>
+        <v>8475.757174</v>
       </c>
       <c r="G63" t="n">
-        <v>10687.878519</v>
+        <v>10665.742051</v>
       </c>
       <c r="H63" t="n">
-        <v>12381.504392</v>
+        <v>12348.316155</v>
       </c>
       <c r="I63" t="n">
-        <v>14017.00295</v>
+        <v>13971.390875</v>
       </c>
       <c r="J63" t="n">
         <v>17013.821876</v>
@@ -5238,19 +5238,19 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>10.076411</v>
+        <v>9.950475000000001</v>
       </c>
       <c r="F64" t="n">
-        <v>14.313236</v>
+        <v>13.990874</v>
       </c>
       <c r="G64" t="n">
-        <v>22.724586</v>
+        <v>22.052465</v>
       </c>
       <c r="H64" t="n">
-        <v>35.608177</v>
+        <v>34.432086</v>
       </c>
       <c r="I64" t="n">
-        <v>60.428693</v>
+        <v>58.619728</v>
       </c>
       <c r="J64" t="n">
         <v>141.258274</v>
@@ -5314,19 +5314,19 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4870.191132</v>
+        <v>4859.487439</v>
       </c>
       <c r="F65" t="n">
-        <v>6634.3371</v>
+        <v>6604.339416</v>
       </c>
       <c r="G65" t="n">
-        <v>9597.955723999999</v>
+        <v>9531.457608000001</v>
       </c>
       <c r="H65" t="n">
-        <v>13097.757935</v>
+        <v>12973.675427</v>
       </c>
       <c r="I65" t="n">
-        <v>18089.525217</v>
+        <v>17884.916806</v>
       </c>
       <c r="J65" t="n">
         <v>30614.852425</v>
@@ -5390,19 +5390,19 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>3438.358764</v>
+        <v>3435.677761</v>
       </c>
       <c r="F66" t="n">
-        <v>4429.613652</v>
+        <v>4423.046744</v>
       </c>
       <c r="G66" t="n">
-        <v>5990.995351</v>
+        <v>5979.204756</v>
       </c>
       <c r="H66" t="n">
-        <v>7472.551836</v>
+        <v>7454.956114</v>
       </c>
       <c r="I66" t="n">
-        <v>8972.818321999999</v>
+        <v>8948.929770999999</v>
       </c>
       <c r="J66" t="n">
         <v>11232.116064</v>
@@ -5466,19 +5466,19 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1185.397996</v>
+        <v>1181.023647</v>
       </c>
       <c r="F67" t="n">
-        <v>1654.449564</v>
+        <v>1642.472944</v>
       </c>
       <c r="G67" t="n">
-        <v>2507.340057</v>
+        <v>2481.159235</v>
       </c>
       <c r="H67" t="n">
-        <v>3585.595449</v>
+        <v>3537.840393</v>
       </c>
       <c r="I67" t="n">
-        <v>5198.533237</v>
+        <v>5122.328177</v>
       </c>
       <c r="J67" t="n">
         <v>9391.253215000001</v>
@@ -5542,19 +5542,19 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>3202.600888</v>
+        <v>3203.115398</v>
       </c>
       <c r="F68" t="n">
-        <v>4185.212958</v>
+        <v>4188.613614</v>
       </c>
       <c r="G68" t="n">
-        <v>5860.566748</v>
+        <v>5874.89872</v>
       </c>
       <c r="H68" t="n">
-        <v>7067.324124</v>
+        <v>7104.814323</v>
       </c>
       <c r="I68" t="n">
-        <v>7203.285336</v>
+        <v>7274.556848</v>
       </c>
       <c r="J68" t="n">
         <v>4466.788649</v>
@@ -5618,19 +5618,19 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>16.311816</v>
+        <v>16.076029</v>
       </c>
       <c r="F69" t="n">
-        <v>25.818749</v>
+        <v>25.179989</v>
       </c>
       <c r="G69" t="n">
-        <v>43.955088</v>
+        <v>42.566618</v>
       </c>
       <c r="H69" t="n">
-        <v>72.327414</v>
+        <v>69.823943</v>
       </c>
       <c r="I69" t="n">
-        <v>127.53347</v>
+        <v>123.597393</v>
       </c>
       <c r="J69" t="n">
         <v>309.61235</v>
@@ -5694,19 +5694,19 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1311.72593</v>
+        <v>1309.334981</v>
       </c>
       <c r="F70" t="n">
-        <v>1664.594918</v>
+        <v>1658.463564</v>
       </c>
       <c r="G70" t="n">
-        <v>2238.44505</v>
+        <v>2226.207941</v>
       </c>
       <c r="H70" t="n">
-        <v>2797.674334</v>
+        <v>2777.255408</v>
       </c>
       <c r="I70" t="n">
-        <v>3477.747062</v>
+        <v>3447.511773</v>
       </c>
       <c r="J70" t="n">
         <v>5052.471844</v>
@@ -5770,19 +5770,19 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>3929.980084</v>
+        <v>3929.644531</v>
       </c>
       <c r="F71" t="n">
-        <v>5260.24878</v>
+        <v>5261.466206</v>
       </c>
       <c r="G71" t="n">
-        <v>6748.969362</v>
+        <v>6756.123101</v>
       </c>
       <c r="H71" t="n">
-        <v>7583.925864</v>
+        <v>7601.910651</v>
       </c>
       <c r="I71" t="n">
-        <v>7798.97232</v>
+        <v>7830.830887</v>
       </c>
       <c r="J71" t="n">
         <v>6929.390731</v>
@@ -5846,19 +5846,19 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1807.260312</v>
+        <v>1803.031839</v>
       </c>
       <c r="F72" t="n">
-        <v>2150.245629</v>
+        <v>2139.623323</v>
       </c>
       <c r="G72" t="n">
-        <v>2753.238234</v>
+        <v>2732.12153</v>
       </c>
       <c r="H72" t="n">
-        <v>3366.427081</v>
+        <v>3331.151472</v>
       </c>
       <c r="I72" t="n">
-        <v>4246.573772</v>
+        <v>4194.357529</v>
       </c>
       <c r="J72" t="n">
         <v>6676.56091</v>
@@ -5922,19 +5922,19 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>34104.54976</v>
+        <v>34142.799907</v>
       </c>
       <c r="F73" t="n">
-        <v>31083.273228</v>
+        <v>31173.395228</v>
       </c>
       <c r="G73" t="n">
-        <v>26877.833141</v>
+        <v>27037.551134</v>
       </c>
       <c r="H73" t="n">
-        <v>21772.523659</v>
+        <v>22014.715098</v>
       </c>
       <c r="I73" t="n">
-        <v>16260.01964</v>
+        <v>16605.355336</v>
       </c>
       <c r="J73" t="n">
         <v>1971.898843</v>
@@ -5998,19 +5998,19 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>8.493852</v>
+        <v>8.371203</v>
       </c>
       <c r="F74" t="n">
-        <v>14.671153</v>
+        <v>14.329664</v>
       </c>
       <c r="G74" t="n">
-        <v>24.806598</v>
+        <v>24.071579</v>
       </c>
       <c r="H74" t="n">
-        <v>39.156917</v>
+        <v>37.865835</v>
       </c>
       <c r="I74" t="n">
-        <v>65.76208</v>
+        <v>63.793101</v>
       </c>
       <c r="J74" t="n">
         <v>152.062485</v>
@@ -6074,58 +6074,58 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1299.914272</v>
+        <v>1287.061968</v>
       </c>
       <c r="F75" t="n">
-        <v>1486.094667</v>
+        <v>1465.971632</v>
       </c>
       <c r="G75" t="n">
-        <v>1835.938255</v>
+        <v>1807.855696</v>
       </c>
       <c r="H75" t="n">
-        <v>1968.689632</v>
+        <v>1934.434918</v>
       </c>
       <c r="I75" t="n">
-        <v>2016.252577</v>
+        <v>1975.904755</v>
       </c>
       <c r="J75" t="n">
-        <v>2040.832664</v>
+        <v>1994.21889</v>
       </c>
       <c r="K75" t="n">
-        <v>2072.533709</v>
+        <v>2019.405375</v>
       </c>
       <c r="L75" t="n">
-        <v>2102.019604</v>
+        <v>2042.577958</v>
       </c>
       <c r="M75" t="n">
-        <v>2105.844024</v>
+        <v>2041.1805</v>
       </c>
       <c r="N75" t="n">
-        <v>2088.674013</v>
+        <v>2020.003451</v>
       </c>
       <c r="O75" t="n">
-        <v>2061.927953</v>
+        <v>1990.27124</v>
       </c>
       <c r="P75" t="n">
-        <v>2031.599643</v>
+        <v>1957.816803</v>
       </c>
       <c r="Q75" t="n">
-        <v>1996.895007</v>
+        <v>1921.857658</v>
       </c>
       <c r="R75" t="n">
-        <v>1971.689837</v>
+        <v>1895.719261</v>
       </c>
       <c r="S75" t="n">
-        <v>1956.20319</v>
+        <v>1879.628012</v>
       </c>
       <c r="T75" t="n">
-        <v>1962.790143</v>
+        <v>1885.600367</v>
       </c>
       <c r="U75" t="n">
-        <v>1996.396159</v>
+        <v>1918.757774</v>
       </c>
       <c r="V75" t="n">
-        <v>2057.582528</v>
+        <v>1980.397377</v>
       </c>
     </row>
     <row r="76">
@@ -6150,58 +6150,58 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>10993.640771</v>
+        <v>10963.837587</v>
       </c>
       <c r="F76" t="n">
-        <v>12552.174508</v>
+        <v>12504.074781</v>
       </c>
       <c r="G76" t="n">
-        <v>12683.326421</v>
+        <v>12605.123343</v>
       </c>
       <c r="H76" t="n">
-        <v>11609.596542</v>
+        <v>11502.749902</v>
       </c>
       <c r="I76" t="n">
-        <v>10937.595308</v>
+        <v>10802.089711</v>
       </c>
       <c r="J76" t="n">
-        <v>10856.928649</v>
+        <v>10692.212883</v>
       </c>
       <c r="K76" t="n">
-        <v>11158.057025</v>
+        <v>10962.752154</v>
       </c>
       <c r="L76" t="n">
-        <v>11599.16834</v>
+        <v>11373.261227</v>
       </c>
       <c r="M76" t="n">
-        <v>11826.70309</v>
+        <v>11572.943586</v>
       </c>
       <c r="N76" t="n">
-        <v>11874.204456</v>
+        <v>11596.151585</v>
       </c>
       <c r="O76" t="n">
-        <v>11698.270542</v>
+        <v>11399.254109</v>
       </c>
       <c r="P76" t="n">
-        <v>11394.697809</v>
+        <v>11077.969155</v>
       </c>
       <c r="Q76" t="n">
-        <v>11001.278972</v>
+        <v>10670.331738</v>
       </c>
       <c r="R76" t="n">
-        <v>10647.094639</v>
+        <v>10303.315416</v>
       </c>
       <c r="S76" t="n">
-        <v>10396.967641</v>
+        <v>10042.338998</v>
       </c>
       <c r="T76" t="n">
-        <v>10329.122013</v>
+        <v>9964.80291</v>
       </c>
       <c r="U76" t="n">
-        <v>10441.526368</v>
+        <v>10070.252919</v>
       </c>
       <c r="V76" t="n">
-        <v>10684.455835</v>
+        <v>10313.156157</v>
       </c>
     </row>
     <row r="77">
@@ -6226,58 +6226,58 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>4994.890086</v>
+        <v>4985.421358</v>
       </c>
       <c r="F77" t="n">
-        <v>6210.444454</v>
+        <v>6199.194683</v>
       </c>
       <c r="G77" t="n">
-        <v>7858.240004</v>
+        <v>7846.206454</v>
       </c>
       <c r="H77" t="n">
-        <v>7998.25858</v>
+        <v>7983.960048</v>
       </c>
       <c r="I77" t="n">
-        <v>7401.570254</v>
+        <v>7382.518066</v>
       </c>
       <c r="J77" t="n">
-        <v>6706.281279</v>
+        <v>6681.587295</v>
       </c>
       <c r="K77" t="n">
-        <v>6205.433299</v>
+        <v>6175.397262</v>
       </c>
       <c r="L77" t="n">
-        <v>5891.991607</v>
+        <v>5857.759249</v>
       </c>
       <c r="M77" t="n">
-        <v>5635.00228</v>
+        <v>5598.140772</v>
       </c>
       <c r="N77" t="n">
-        <v>5375.745873</v>
+        <v>5337.414906</v>
       </c>
       <c r="O77" t="n">
-        <v>5093.715165</v>
+        <v>5054.450657</v>
       </c>
       <c r="P77" t="n">
-        <v>4806.107624</v>
+        <v>4766.173145</v>
       </c>
       <c r="Q77" t="n">
-        <v>4526.720337</v>
+        <v>4486.468047</v>
       </c>
       <c r="R77" t="n">
-        <v>4291.189764</v>
+        <v>4250.818586</v>
       </c>
       <c r="S77" t="n">
-        <v>4090.300753</v>
+        <v>4050.064371</v>
       </c>
       <c r="T77" t="n">
-        <v>3934.352664</v>
+        <v>3894.329897</v>
       </c>
       <c r="U77" t="n">
-        <v>3816.465452</v>
+        <v>3776.805603</v>
       </c>
       <c r="V77" t="n">
-        <v>3720.771587</v>
+        <v>3682.013224</v>
       </c>
     </row>
     <row r="78">
@@ -6302,58 +6302,58 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>92486.88267599999</v>
+        <v>92629.786741</v>
       </c>
       <c r="F78" t="n">
-        <v>87436.246073</v>
+        <v>87628.845057</v>
       </c>
       <c r="G78" t="n">
-        <v>89419.62285099999</v>
+        <v>89636.461459</v>
       </c>
       <c r="H78" t="n">
-        <v>84290.15147300001</v>
+        <v>84504.535965</v>
       </c>
       <c r="I78" t="n">
-        <v>80118.87395199999</v>
+        <v>80338.194424</v>
       </c>
       <c r="J78" t="n">
-        <v>78049.569062</v>
+        <v>78289.217042</v>
       </c>
       <c r="K78" t="n">
-        <v>77923.30979</v>
+        <v>78198.54759</v>
       </c>
       <c r="L78" t="n">
-        <v>78299.779899</v>
+        <v>78619.207564</v>
       </c>
       <c r="M78" t="n">
-        <v>77809.595384</v>
+        <v>78173.73739900001</v>
       </c>
       <c r="N78" t="n">
-        <v>76303.227442</v>
+        <v>76708.397342</v>
       </c>
       <c r="O78" t="n">
-        <v>73975.30458900001</v>
+        <v>74417.188176</v>
       </c>
       <c r="P78" t="n">
-        <v>71077.04678600001</v>
+        <v>71550.16485</v>
       </c>
       <c r="Q78" t="n">
-        <v>67747.872967</v>
+        <v>68247.100185</v>
       </c>
       <c r="R78" t="n">
-        <v>64498.849874</v>
+        <v>65023.830389</v>
       </c>
       <c r="S78" t="n">
-        <v>61225.02157</v>
+        <v>61775.905468</v>
       </c>
       <c r="T78" t="n">
-        <v>58072.94491</v>
+        <v>58651.64332</v>
       </c>
       <c r="U78" t="n">
-        <v>54887.712979</v>
+        <v>55493.741269</v>
       </c>
       <c r="V78" t="n">
-        <v>51363.177888</v>
+        <v>51989.084602</v>
       </c>
     </row>
     <row r="79">
@@ -6378,58 +6378,58 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>3489.510903</v>
+        <v>3472.692835</v>
       </c>
       <c r="F79" t="n">
-        <v>5014.783992</v>
+        <v>4989.703422</v>
       </c>
       <c r="G79" t="n">
-        <v>7836.72532</v>
+        <v>7806.03653</v>
       </c>
       <c r="H79" t="n">
-        <v>9993.886356999999</v>
+        <v>9961.645796000001</v>
       </c>
       <c r="I79" t="n">
-        <v>11376.560022</v>
+        <v>11342.73325</v>
       </c>
       <c r="J79" t="n">
-        <v>12125.972693</v>
+        <v>12089.285318</v>
       </c>
       <c r="K79" t="n">
-        <v>12557.566734</v>
+        <v>12516.525299</v>
       </c>
       <c r="L79" t="n">
-        <v>12760.524177</v>
+        <v>12714.109257</v>
       </c>
       <c r="M79" t="n">
-        <v>12696.52229</v>
+        <v>12644.715407</v>
       </c>
       <c r="N79" t="n">
-        <v>12446.699706</v>
+        <v>12390.107974</v>
       </c>
       <c r="O79" t="n">
-        <v>12110.693067</v>
+        <v>12050.312341</v>
       </c>
       <c r="P79" t="n">
-        <v>11748.209312</v>
+        <v>11685.173459</v>
       </c>
       <c r="Q79" t="n">
-        <v>11359.106126</v>
+        <v>11294.512506</v>
       </c>
       <c r="R79" t="n">
-        <v>11005.127106</v>
+        <v>10939.49213</v>
       </c>
       <c r="S79" t="n">
-        <v>10659.397819</v>
+        <v>10593.265115</v>
       </c>
       <c r="T79" t="n">
-        <v>10355.26015</v>
+        <v>10289.035207</v>
       </c>
       <c r="U79" t="n">
-        <v>10086.87064</v>
+        <v>10021.163741</v>
       </c>
       <c r="V79" t="n">
-        <v>9823.206491999999</v>
+        <v>9759.263864</v>
       </c>
     </row>
     <row r="80">
@@ -6454,58 +6454,58 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>3261.647052</v>
+        <v>3256.397244</v>
       </c>
       <c r="F80" t="n">
-        <v>3101.923688</v>
+        <v>3091.565885</v>
       </c>
       <c r="G80" t="n">
-        <v>3306.979306</v>
+        <v>3289.911689</v>
       </c>
       <c r="H80" t="n">
-        <v>3336.332568</v>
+        <v>3313.222957</v>
       </c>
       <c r="I80" t="n">
-        <v>3415.949023</v>
+        <v>3386.804877</v>
       </c>
       <c r="J80" t="n">
-        <v>3575.044986</v>
+        <v>3539.610279</v>
       </c>
       <c r="K80" t="n">
-        <v>3817.947777</v>
+        <v>3775.888882</v>
       </c>
       <c r="L80" t="n">
-        <v>4082.55455</v>
+        <v>4033.931908</v>
       </c>
       <c r="M80" t="n">
-        <v>4292.600635</v>
+        <v>4238.343967</v>
       </c>
       <c r="N80" t="n">
-        <v>4434.773175</v>
+        <v>4376.031915</v>
       </c>
       <c r="O80" t="n">
-        <v>4527.171944</v>
+        <v>4465.011918</v>
       </c>
       <c r="P80" t="n">
-        <v>4592.507347</v>
+        <v>4527.753736</v>
       </c>
       <c r="Q80" t="n">
-        <v>4630.766186</v>
+        <v>4564.134935</v>
       </c>
       <c r="R80" t="n">
-        <v>4665.746449</v>
+        <v>4597.454077</v>
       </c>
       <c r="S80" t="n">
-        <v>4686.262813</v>
+        <v>4616.609511</v>
       </c>
       <c r="T80" t="n">
-        <v>4709.429306</v>
+        <v>4638.60442</v>
       </c>
       <c r="U80" t="n">
-        <v>4736.299471</v>
+        <v>4664.79146</v>
       </c>
       <c r="V80" t="n">
-        <v>4756.50019</v>
+        <v>4685.503667</v>
       </c>
     </row>
     <row r="81">
@@ -6530,58 +6530,58 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1458.078731</v>
+        <v>1428.679925</v>
       </c>
       <c r="F81" t="n">
-        <v>2242.590332</v>
+        <v>2192.122698</v>
       </c>
       <c r="G81" t="n">
-        <v>3581.22789</v>
+        <v>3504.678704</v>
       </c>
       <c r="H81" t="n">
-        <v>4718.046101</v>
+        <v>4618.09</v>
       </c>
       <c r="I81" t="n">
-        <v>5641.250917</v>
+        <v>5516.495805</v>
       </c>
       <c r="J81" t="n">
-        <v>6397.52538</v>
+        <v>6244.809611</v>
       </c>
       <c r="K81" t="n">
-        <v>7108.327403</v>
+        <v>6923.093875</v>
       </c>
       <c r="L81" t="n">
-        <v>7813.025824</v>
+        <v>7591.507409</v>
       </c>
       <c r="M81" t="n">
-        <v>8442.88906</v>
+        <v>8185.278648</v>
       </c>
       <c r="N81" t="n">
-        <v>8997.579223999999</v>
+        <v>8705.668682</v>
       </c>
       <c r="O81" t="n">
-        <v>9592.813491999999</v>
+        <v>9267.193756000001</v>
       </c>
       <c r="P81" t="n">
-        <v>10254.396398</v>
+        <v>9894.427417999999</v>
       </c>
       <c r="Q81" t="n">
-        <v>10983.424006</v>
+        <v>10587.931545</v>
       </c>
       <c r="R81" t="n">
-        <v>11850.857359</v>
+        <v>11415.634917</v>
       </c>
       <c r="S81" t="n">
-        <v>12860.55505</v>
+        <v>12382.269559</v>
       </c>
       <c r="T81" t="n">
-        <v>14089.590806</v>
+        <v>13563.844347</v>
       </c>
       <c r="U81" t="n">
-        <v>15599.113003</v>
+        <v>15023.043562</v>
       </c>
       <c r="V81" t="n">
-        <v>17447.653569</v>
+        <v>16824.142256</v>
       </c>
     </row>
     <row r="82">
@@ -6606,58 +6606,58 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>15724.77528</v>
+        <v>15737.059052</v>
       </c>
       <c r="F82" t="n">
-        <v>17271.587121</v>
+        <v>17292.997868</v>
       </c>
       <c r="G82" t="n">
-        <v>20273.429259</v>
+        <v>20303.483742</v>
       </c>
       <c r="H82" t="n">
-        <v>21265.873645</v>
+        <v>21301.696742</v>
       </c>
       <c r="I82" t="n">
-        <v>21629.844445</v>
+        <v>21671.990867</v>
       </c>
       <c r="J82" t="n">
-        <v>21867.645039</v>
+        <v>21918.300539</v>
       </c>
       <c r="K82" t="n">
-        <v>22163.868801</v>
+        <v>22224.992901</v>
       </c>
       <c r="L82" t="n">
-        <v>22374.254234</v>
+        <v>22446.98937</v>
       </c>
       <c r="M82" t="n">
-        <v>22191.793187</v>
+        <v>22275.434083</v>
       </c>
       <c r="N82" t="n">
-        <v>21644.189179</v>
+        <v>21737.401734</v>
       </c>
       <c r="O82" t="n">
-        <v>20847.655144</v>
+        <v>20949.238195</v>
       </c>
       <c r="P82" t="n">
-        <v>19938.226495</v>
+        <v>20047.53204</v>
       </c>
       <c r="Q82" t="n">
-        <v>18946.509494</v>
+        <v>19062.83292</v>
       </c>
       <c r="R82" t="n">
-        <v>17992.781275</v>
+        <v>18116.067834</v>
       </c>
       <c r="S82" t="n">
-        <v>17030.178885</v>
+        <v>17160.052539</v>
       </c>
       <c r="T82" t="n">
-        <v>16105.088096</v>
+        <v>16241.551062</v>
       </c>
       <c r="U82" t="n">
-        <v>15191.513613</v>
+        <v>15334.23461</v>
       </c>
       <c r="V82" t="n">
-        <v>14222.115993</v>
+        <v>14369.388368</v>
       </c>
     </row>
     <row r="83">
@@ -6682,58 +6682,58 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>32191.671104</v>
+        <v>32140.074164</v>
       </c>
       <c r="F83" t="n">
-        <v>47003.26343</v>
+        <v>46954.632237</v>
       </c>
       <c r="G83" t="n">
-        <v>72589.55506699999</v>
+        <v>72585.286758</v>
       </c>
       <c r="H83" t="n">
-        <v>90698.25505199999</v>
+        <v>90758.753621</v>
       </c>
       <c r="I83" t="n">
-        <v>100800.624418</v>
+        <v>100921.789159</v>
       </c>
       <c r="J83" t="n">
-        <v>105042.599186</v>
+        <v>105213.157082</v>
       </c>
       <c r="K83" t="n">
-        <v>106704.526378</v>
+        <v>106914.967578</v>
       </c>
       <c r="L83" t="n">
-        <v>106844.735315</v>
+        <v>107088.709608</v>
       </c>
       <c r="M83" t="n">
-        <v>105002.907098</v>
+        <v>105274.082687</v>
       </c>
       <c r="N83" t="n">
-        <v>101675.526217</v>
+        <v>101969.441695</v>
       </c>
       <c r="O83" t="n">
-        <v>97527.63069400001</v>
+        <v>97842.262199</v>
       </c>
       <c r="P83" t="n">
-        <v>93121.977896</v>
+        <v>93457.75870400001</v>
       </c>
       <c r="Q83" t="n">
-        <v>88540.411652</v>
+        <v>88897.81521299999</v>
       </c>
       <c r="R83" t="n">
-        <v>84260.629174</v>
+        <v>84641.632868</v>
       </c>
       <c r="S83" t="n">
-        <v>80011.94725</v>
+        <v>80416.701399</v>
       </c>
       <c r="T83" t="n">
-        <v>75997.297867</v>
+        <v>76426.464425</v>
       </c>
       <c r="U83" t="n">
-        <v>72123.049873</v>
+        <v>72576.156619</v>
       </c>
       <c r="V83" t="n">
-        <v>68113.032186</v>
+        <v>68585.546755</v>
       </c>
     </row>
     <row r="84">
@@ -6910,58 +6910,58 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>10010.93741</v>
+        <v>10010.799992</v>
       </c>
       <c r="F86" t="n">
-        <v>9849.732002000001</v>
+        <v>9849.515085000001</v>
       </c>
       <c r="G86" t="n">
-        <v>10649.136397</v>
+        <v>10648.78787</v>
       </c>
       <c r="H86" t="n">
-        <v>10507.303944</v>
+        <v>10506.796876</v>
       </c>
       <c r="I86" t="n">
-        <v>10205.000736</v>
+        <v>10204.30431</v>
       </c>
       <c r="J86" t="n">
-        <v>9924.265647</v>
+        <v>9923.350138</v>
       </c>
       <c r="K86" t="n">
-        <v>9806.288368</v>
+        <v>9805.110891</v>
       </c>
       <c r="L86" t="n">
-        <v>9803.615413</v>
+        <v>9802.1281</v>
       </c>
       <c r="M86" t="n">
-        <v>9644.417589000001</v>
+        <v>9642.621752999999</v>
       </c>
       <c r="N86" t="n">
-        <v>9318.537617</v>
+        <v>9316.458745</v>
       </c>
       <c r="O86" t="n">
-        <v>8977.325307999999</v>
+        <v>8974.98083</v>
       </c>
       <c r="P86" t="n">
-        <v>8582.765509999999</v>
+        <v>8580.174881999999</v>
       </c>
       <c r="Q86" t="n">
-        <v>8151.9282</v>
+        <v>8149.105696</v>
       </c>
       <c r="R86" t="n">
-        <v>7729.339844</v>
+        <v>7726.288254</v>
       </c>
       <c r="S86" t="n">
-        <v>7316.158007</v>
+        <v>7312.885123</v>
       </c>
       <c r="T86" t="n">
-        <v>6917.719743</v>
+        <v>6914.228021</v>
       </c>
       <c r="U86" t="n">
-        <v>6524.862271</v>
+        <v>6521.150405</v>
       </c>
       <c r="V86" t="n">
-        <v>6110.679289</v>
+        <v>6106.754334</v>
       </c>
     </row>
     <row r="87">
@@ -6986,58 +6986,58 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1552.661101</v>
+        <v>1552.592736</v>
       </c>
       <c r="F87" t="n">
-        <v>1719.466148</v>
+        <v>1719.350406</v>
       </c>
       <c r="G87" t="n">
-        <v>2136.126168</v>
+        <v>2135.972609</v>
       </c>
       <c r="H87" t="n">
-        <v>2368.230017</v>
+        <v>2368.05365</v>
       </c>
       <c r="I87" t="n">
-        <v>2524.499783</v>
+        <v>2524.296512</v>
       </c>
       <c r="J87" t="n">
-        <v>2647.639753</v>
+        <v>2647.397015</v>
       </c>
       <c r="K87" t="n">
-        <v>2786.603057</v>
+        <v>2786.300802</v>
       </c>
       <c r="L87" t="n">
-        <v>2942.152603</v>
+        <v>2941.769816</v>
       </c>
       <c r="M87" t="n">
-        <v>3034.18547</v>
+        <v>3033.713335</v>
       </c>
       <c r="N87" t="n">
-        <v>3054.001379</v>
+        <v>3053.438628</v>
       </c>
       <c r="O87" t="n">
-        <v>3048.671604</v>
+        <v>3048.018603</v>
       </c>
       <c r="P87" t="n">
-        <v>3006.930556</v>
+        <v>3006.193022</v>
       </c>
       <c r="Q87" t="n">
-        <v>2935.775051</v>
+        <v>2934.961657</v>
       </c>
       <c r="R87" t="n">
-        <v>2852.622327</v>
+        <v>2851.742027</v>
       </c>
       <c r="S87" t="n">
-        <v>2759.493963</v>
+        <v>2758.557156</v>
       </c>
       <c r="T87" t="n">
-        <v>2660.581016</v>
+        <v>2659.591996</v>
       </c>
       <c r="U87" t="n">
-        <v>2557.568503</v>
+        <v>2556.529406</v>
       </c>
       <c r="V87" t="n">
-        <v>2443.006788</v>
+        <v>2441.920428</v>
       </c>
     </row>
     <row r="88">
@@ -7062,58 +7062,58 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>24005.464023</v>
+        <v>24006.411212</v>
       </c>
       <c r="F88" t="n">
-        <v>21506.18027</v>
+        <v>21507.212445</v>
       </c>
       <c r="G88" t="n">
-        <v>21924.453915</v>
+        <v>21925.281226</v>
       </c>
       <c r="H88" t="n">
-        <v>21454.44934</v>
+        <v>21455.021668</v>
       </c>
       <c r="I88" t="n">
-        <v>21329.403532</v>
+        <v>21329.876842</v>
       </c>
       <c r="J88" t="n">
-        <v>21624.357689</v>
+        <v>21624.909419</v>
       </c>
       <c r="K88" t="n">
-        <v>22461.640927</v>
+        <v>22462.403599</v>
       </c>
       <c r="L88" t="n">
-        <v>23647.260148</v>
+        <v>23648.329991</v>
       </c>
       <c r="M88" t="n">
-        <v>24444.373518</v>
+        <v>24445.802642</v>
       </c>
       <c r="N88" t="n">
-        <v>24739.843771</v>
+        <v>24741.667253</v>
       </c>
       <c r="O88" t="n">
-        <v>24874.720816</v>
+        <v>24876.979516</v>
       </c>
       <c r="P88" t="n">
-        <v>24741.291344</v>
+        <v>24743.967925</v>
       </c>
       <c r="Q88" t="n">
-        <v>24398.067749</v>
+        <v>24401.121049</v>
       </c>
       <c r="R88" t="n">
-        <v>23991.623954</v>
+        <v>23995.017514</v>
       </c>
       <c r="S88" t="n">
-        <v>23527.244279</v>
+        <v>23530.936779</v>
       </c>
       <c r="T88" t="n">
-        <v>23061.318093</v>
+        <v>23065.315414</v>
       </c>
       <c r="U88" t="n">
-        <v>22594.225514</v>
+        <v>22598.544304</v>
       </c>
       <c r="V88" t="n">
-        <v>22038.575786</v>
+        <v>22043.198647</v>
       </c>
     </row>
     <row r="89">
@@ -7138,58 +7138,58 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6732.666668</v>
+        <v>6733.437367</v>
       </c>
       <c r="F89" t="n">
-        <v>6381.86029</v>
+        <v>6383.176459</v>
       </c>
       <c r="G89" t="n">
-        <v>6977.350912</v>
+        <v>6979.380709</v>
       </c>
       <c r="H89" t="n">
-        <v>7001.11227</v>
+        <v>7003.734785</v>
       </c>
       <c r="I89" t="n">
-        <v>6922.822763</v>
+        <v>6925.998732</v>
       </c>
       <c r="J89" t="n">
-        <v>6857.041711</v>
+        <v>6860.761268</v>
       </c>
       <c r="K89" t="n">
-        <v>6909.89939</v>
+        <v>6914.217591</v>
       </c>
       <c r="L89" t="n">
-        <v>7052.252562</v>
+        <v>7057.240157</v>
       </c>
       <c r="M89" t="n">
-        <v>7084.517503</v>
+        <v>7090.109365</v>
       </c>
       <c r="N89" t="n">
-        <v>6999.951561</v>
+        <v>7006.043783</v>
       </c>
       <c r="O89" t="n">
-        <v>6914.904836</v>
+        <v>6921.467002</v>
       </c>
       <c r="P89" t="n">
-        <v>6804.769553</v>
+        <v>6811.749334</v>
       </c>
       <c r="Q89" t="n">
-        <v>6675.598351</v>
+        <v>6682.957941</v>
       </c>
       <c r="R89" t="n">
-        <v>6551.294887</v>
+        <v>6559.032982</v>
       </c>
       <c r="S89" t="n">
-        <v>6426.247731</v>
+        <v>6434.366611</v>
       </c>
       <c r="T89" t="n">
-        <v>6306.290503</v>
+        <v>6314.796288</v>
       </c>
       <c r="U89" t="n">
-        <v>6188.366595</v>
+        <v>6197.254761</v>
       </c>
       <c r="V89" t="n">
-        <v>6051.36879</v>
+        <v>6060.596516</v>
       </c>
     </row>
     <row r="90">
@@ -7214,58 +7214,58 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>12454.395803</v>
+        <v>12453.84121</v>
       </c>
       <c r="F90" t="n">
-        <v>12014.09573</v>
+        <v>12013.034368</v>
       </c>
       <c r="G90" t="n">
-        <v>13468.340176</v>
+        <v>13466.769956</v>
       </c>
       <c r="H90" t="n">
-        <v>13960.378815</v>
+        <v>13958.484749</v>
       </c>
       <c r="I90" t="n">
-        <v>14193.457104</v>
+        <v>14191.319012</v>
       </c>
       <c r="J90" t="n">
-        <v>14332.449186</v>
+        <v>14330.085971</v>
       </c>
       <c r="K90" t="n">
-        <v>14607.634101</v>
+        <v>14605.012093</v>
       </c>
       <c r="L90" t="n">
-        <v>15018.418703</v>
+        <v>15015.519318</v>
       </c>
       <c r="M90" t="n">
-        <v>15178.572347</v>
+        <v>15175.487342</v>
       </c>
       <c r="N90" t="n">
-        <v>15029.082034</v>
+        <v>15025.909071</v>
       </c>
       <c r="O90" t="n">
-        <v>14784.254389</v>
+        <v>14781.02183</v>
       </c>
       <c r="P90" t="n">
-        <v>14388.867835</v>
+        <v>14385.591057</v>
       </c>
       <c r="Q90" t="n">
-        <v>13901.024599</v>
+        <v>13897.712759</v>
       </c>
       <c r="R90" t="n">
-        <v>13420.588264</v>
+        <v>13417.242733</v>
       </c>
       <c r="S90" t="n">
-        <v>12960.059839</v>
+        <v>12956.703162</v>
       </c>
       <c r="T90" t="n">
-        <v>12533.549711</v>
+        <v>12530.208029</v>
       </c>
       <c r="U90" t="n">
-        <v>12123.894564</v>
+        <v>12120.576012</v>
       </c>
       <c r="V90" t="n">
-        <v>11678.282002</v>
+        <v>11674.979729</v>
       </c>
     </row>
     <row r="91">
@@ -7290,58 +7290,58 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>5601.215954</v>
+        <v>5601.294391</v>
       </c>
       <c r="F91" t="n">
-        <v>5511.10309</v>
+        <v>5511.251869</v>
       </c>
       <c r="G91" t="n">
-        <v>6024.672455</v>
+        <v>6024.911646</v>
       </c>
       <c r="H91" t="n">
-        <v>5913.480975</v>
+        <v>5913.750769</v>
       </c>
       <c r="I91" t="n">
-        <v>5631.916817</v>
+        <v>5632.16044</v>
       </c>
       <c r="J91" t="n">
-        <v>5328.414496</v>
+        <v>5328.58939</v>
       </c>
       <c r="K91" t="n">
-        <v>5117.325444</v>
+        <v>5117.409863</v>
       </c>
       <c r="L91" t="n">
-        <v>4986.553441</v>
+        <v>4986.542436</v>
       </c>
       <c r="M91" t="n">
-        <v>4789.03733</v>
+        <v>4788.932491</v>
       </c>
       <c r="N91" t="n">
-        <v>4520.604768</v>
+        <v>4520.414127</v>
       </c>
       <c r="O91" t="n">
-        <v>4261.916725</v>
+        <v>4261.638931</v>
       </c>
       <c r="P91" t="n">
-        <v>3994.319127</v>
+        <v>3993.950179</v>
       </c>
       <c r="Q91" t="n">
-        <v>3726.002424</v>
+        <v>3725.536801</v>
       </c>
       <c r="R91" t="n">
-        <v>3490.029861</v>
+        <v>3489.481232</v>
       </c>
       <c r="S91" t="n">
-        <v>3292.571095</v>
+        <v>3291.967738</v>
       </c>
       <c r="T91" t="n">
-        <v>3135.327014</v>
+        <v>3134.696741</v>
       </c>
       <c r="U91" t="n">
-        <v>3009.475434</v>
+        <v>3008.836549</v>
       </c>
       <c r="V91" t="n">
-        <v>2896.737292</v>
+        <v>2896.100465</v>
       </c>
     </row>
     <row r="92">
@@ -7366,58 +7366,58 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1325.721818</v>
+        <v>1325.381341</v>
       </c>
       <c r="F92" t="n">
-        <v>1327.197117</v>
+        <v>1326.597994</v>
       </c>
       <c r="G92" t="n">
-        <v>1508.304124</v>
+        <v>1507.400418</v>
       </c>
       <c r="H92" t="n">
-        <v>1532.58399</v>
+        <v>1531.433227</v>
       </c>
       <c r="I92" t="n">
-        <v>1505.809385</v>
+        <v>1504.427387</v>
       </c>
       <c r="J92" t="n">
-        <v>1467.24984</v>
+        <v>1465.638751</v>
       </c>
       <c r="K92" t="n">
-        <v>1446.700466</v>
+        <v>1444.842001</v>
       </c>
       <c r="L92" t="n">
-        <v>1439.649316</v>
+        <v>1437.523915</v>
       </c>
       <c r="M92" t="n">
-        <v>1409.826305</v>
+        <v>1407.477329</v>
       </c>
       <c r="N92" t="n">
-        <v>1354.597965</v>
+        <v>1352.086594</v>
       </c>
       <c r="O92" t="n">
-        <v>1296.496637</v>
+        <v>1293.852921</v>
       </c>
       <c r="P92" t="n">
-        <v>1230.895017</v>
+        <v>1228.157109</v>
       </c>
       <c r="Q92" t="n">
-        <v>1162.955042</v>
+        <v>1160.155382</v>
       </c>
       <c r="R92" t="n">
-        <v>1101.434387</v>
+        <v>1098.589491</v>
       </c>
       <c r="S92" t="n">
-        <v>1047.570921</v>
+        <v>1044.693303</v>
       </c>
       <c r="T92" t="n">
-        <v>1001.795856</v>
+        <v>998.8905109999999</v>
       </c>
       <c r="U92" t="n">
-        <v>961.746321</v>
+        <v>958.816343</v>
       </c>
       <c r="V92" t="n">
-        <v>922.4531030000001</v>
+        <v>919.5133970000001</v>
       </c>
     </row>
     <row r="93">
@@ -7442,58 +7442,58 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>71.46402500000001</v>
+        <v>71.35439599999999</v>
       </c>
       <c r="F93" t="n">
-        <v>78.315974</v>
+        <v>78.111943</v>
       </c>
       <c r="G93" t="n">
-        <v>97.63088999999999</v>
+        <v>97.303669</v>
       </c>
       <c r="H93" t="n">
-        <v>111.094015</v>
+        <v>110.656434</v>
       </c>
       <c r="I93" t="n">
-        <v>122.276309</v>
+        <v>121.731886</v>
       </c>
       <c r="J93" t="n">
-        <v>131.619089</v>
+        <v>130.969269</v>
       </c>
       <c r="K93" t="n">
-        <v>140.976679</v>
+        <v>140.213491</v>
       </c>
       <c r="L93" t="n">
-        <v>150.541161</v>
+        <v>149.65409</v>
       </c>
       <c r="M93" t="n">
-        <v>156.386103</v>
+        <v>155.389379</v>
       </c>
       <c r="N93" t="n">
-        <v>158.220869</v>
+        <v>157.137753</v>
       </c>
       <c r="O93" t="n">
-        <v>158.789489</v>
+        <v>157.632037</v>
       </c>
       <c r="P93" t="n">
-        <v>157.747873</v>
+        <v>156.533783</v>
       </c>
       <c r="Q93" t="n">
-        <v>155.509783</v>
+        <v>154.25505</v>
       </c>
       <c r="R93" t="n">
-        <v>152.861006</v>
+        <v>151.574619</v>
       </c>
       <c r="S93" t="n">
-        <v>149.821455</v>
+        <v>148.51076</v>
       </c>
       <c r="T93" t="n">
-        <v>146.612894</v>
+        <v>145.282708</v>
       </c>
       <c r="U93" t="n">
-        <v>143.348214</v>
+        <v>142.00206</v>
       </c>
       <c r="V93" t="n">
-        <v>139.701818</v>
+        <v>138.346893</v>
       </c>
     </row>
     <row r="94">
@@ -7518,58 +7518,58 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>56593.495616</v>
+        <v>56592.446314</v>
       </c>
       <c r="F94" t="n">
-        <v>59821.161141</v>
+        <v>59819.982867</v>
       </c>
       <c r="G94" t="n">
-        <v>68457.97835799999</v>
+        <v>68456.827911</v>
       </c>
       <c r="H94" t="n">
-        <v>70290.387605</v>
+        <v>70289.284223</v>
       </c>
       <c r="I94" t="n">
-        <v>69982.33792000001</v>
+        <v>69981.11107499999</v>
       </c>
       <c r="J94" t="n">
-        <v>69236.212184</v>
+        <v>69234.769524</v>
       </c>
       <c r="K94" t="n">
-        <v>69447.424769</v>
+        <v>69445.73826500001</v>
       </c>
       <c r="L94" t="n">
-        <v>70448.681066</v>
+        <v>70446.743428</v>
       </c>
       <c r="M94" t="n">
-        <v>70160.11750399999</v>
+        <v>70157.916816</v>
       </c>
       <c r="N94" t="n">
-        <v>68399.53627900001</v>
+        <v>68397.057025</v>
       </c>
       <c r="O94" t="n">
-        <v>66317.74276199999</v>
+        <v>66314.94087400001</v>
       </c>
       <c r="P94" t="n">
-        <v>63722.664816</v>
+        <v>63719.567555</v>
       </c>
       <c r="Q94" t="n">
-        <v>60815.357014</v>
+        <v>60811.9972</v>
       </c>
       <c r="R94" t="n">
-        <v>57942.813187</v>
+        <v>57939.121975</v>
       </c>
       <c r="S94" t="n">
-        <v>55131.752358</v>
+        <v>55127.588624</v>
       </c>
       <c r="T94" t="n">
-        <v>52494.401843</v>
+        <v>52489.599216</v>
       </c>
       <c r="U94" t="n">
-        <v>50089.03569</v>
+        <v>50083.514241</v>
       </c>
       <c r="V94" t="n">
-        <v>47773.457907</v>
+        <v>47767.249059</v>
       </c>
     </row>
     <row r="95">
@@ -7594,58 +7594,58 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>25657.22602</v>
+        <v>25656.342731</v>
       </c>
       <c r="F95" t="n">
-        <v>27178.173032</v>
+        <v>27177.023759</v>
       </c>
       <c r="G95" t="n">
-        <v>31597.332266</v>
+        <v>31596.182591</v>
       </c>
       <c r="H95" t="n">
-        <v>32778.136543</v>
+        <v>32777.151292</v>
       </c>
       <c r="I95" t="n">
-        <v>32866.93432</v>
+        <v>32866.084663</v>
       </c>
       <c r="J95" t="n">
-        <v>32421.354309</v>
+        <v>32420.485342</v>
       </c>
       <c r="K95" t="n">
-        <v>32061.635304</v>
+        <v>32060.56432</v>
       </c>
       <c r="L95" t="n">
-        <v>31721.639814</v>
+        <v>31720.175434</v>
       </c>
       <c r="M95" t="n">
-        <v>30632.76561</v>
+        <v>30630.830449</v>
       </c>
       <c r="N95" t="n">
-        <v>28853.138243</v>
+        <v>28850.724571</v>
       </c>
       <c r="O95" t="n">
-        <v>27019.194733</v>
+        <v>27016.318793</v>
       </c>
       <c r="P95" t="n">
-        <v>25110.835842</v>
+        <v>25107.555507</v>
       </c>
       <c r="Q95" t="n">
-        <v>23224.562284</v>
+        <v>23220.927679</v>
       </c>
       <c r="R95" t="n">
-        <v>21544.927567</v>
+        <v>21541.018185</v>
       </c>
       <c r="S95" t="n">
-        <v>20085.859472</v>
+        <v>20081.784724</v>
       </c>
       <c r="T95" t="n">
-        <v>18853.947087</v>
+        <v>18849.807135</v>
       </c>
       <c r="U95" t="n">
-        <v>17780.513558</v>
+        <v>17776.363437</v>
       </c>
       <c r="V95" t="n">
-        <v>16766.968506</v>
+        <v>16762.856784</v>
       </c>
     </row>
     <row r="96">
@@ -7670,58 +7670,58 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>17693.241652</v>
+        <v>17694.647267</v>
       </c>
       <c r="F96" t="n">
-        <v>16536.416538</v>
+        <v>16538.65559</v>
       </c>
       <c r="G96" t="n">
-        <v>16939.749492</v>
+        <v>16942.696485</v>
       </c>
       <c r="H96" t="n">
-        <v>16407.601193</v>
+        <v>16411.039601</v>
       </c>
       <c r="I96" t="n">
-        <v>16041.360193</v>
+        <v>16045.342171</v>
       </c>
       <c r="J96" t="n">
-        <v>15958.783702</v>
+        <v>15963.436172</v>
       </c>
       <c r="K96" t="n">
-        <v>16259.466278</v>
+        <v>16264.962729</v>
       </c>
       <c r="L96" t="n">
-        <v>16808.741839</v>
+        <v>16815.248021</v>
       </c>
       <c r="M96" t="n">
-        <v>17060.996447</v>
+        <v>17068.448825</v>
       </c>
       <c r="N96" t="n">
-        <v>16949.657808</v>
+        <v>16957.900909</v>
       </c>
       <c r="O96" t="n">
-        <v>16734.895681</v>
+        <v>16743.846417</v>
       </c>
       <c r="P96" t="n">
-        <v>16363.765664</v>
+        <v>16373.297876</v>
       </c>
       <c r="Q96" t="n">
-        <v>15890.498766</v>
+        <v>15900.516899</v>
       </c>
       <c r="R96" t="n">
-        <v>15410.11982</v>
+        <v>15420.589977</v>
       </c>
       <c r="S96" t="n">
-        <v>14924.036801</v>
+        <v>14934.9304</v>
       </c>
       <c r="T96" t="n">
-        <v>14451.948888</v>
+        <v>14463.242159</v>
       </c>
       <c r="U96" t="n">
-        <v>13994.55675</v>
+        <v>14006.223283</v>
       </c>
       <c r="V96" t="n">
-        <v>13509.048696</v>
+        <v>13521.021129</v>
       </c>
     </row>
     <row r="97">
@@ -7746,58 +7746,58 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>3215.24909</v>
+        <v>3215.190224</v>
       </c>
       <c r="F97" t="n">
-        <v>2794.790411</v>
+        <v>2794.578959</v>
       </c>
       <c r="G97" t="n">
-        <v>2795.646155</v>
+        <v>2795.206218</v>
       </c>
       <c r="H97" t="n">
-        <v>2709.097063</v>
+        <v>2708.448497</v>
       </c>
       <c r="I97" t="n">
-        <v>2686.907592</v>
+        <v>2686.073423</v>
       </c>
       <c r="J97" t="n">
-        <v>2722.674269</v>
+        <v>2721.669617</v>
       </c>
       <c r="K97" t="n">
-        <v>2825.058246</v>
+        <v>2823.877384</v>
       </c>
       <c r="L97" t="n">
-        <v>2971.457016</v>
+        <v>2970.088376</v>
       </c>
       <c r="M97" t="n">
-        <v>3069.657363</v>
+        <v>3068.123365</v>
       </c>
       <c r="N97" t="n">
-        <v>3108.993682</v>
+        <v>3107.327518</v>
       </c>
       <c r="O97" t="n">
-        <v>3136.786048</v>
+        <v>3135.001275</v>
       </c>
       <c r="P97" t="n">
-        <v>3141.757508</v>
+        <v>3139.872415</v>
       </c>
       <c r="Q97" t="n">
-        <v>3128.424972</v>
+        <v>3126.456121</v>
       </c>
       <c r="R97" t="n">
-        <v>3110.498523</v>
+        <v>3108.454637</v>
       </c>
       <c r="S97" t="n">
-        <v>3085.219743</v>
+        <v>3083.111283</v>
       </c>
       <c r="T97" t="n">
-        <v>3054.313607</v>
+        <v>3052.148037</v>
       </c>
       <c r="U97" t="n">
-        <v>3016.260444</v>
+        <v>3014.04306</v>
       </c>
       <c r="V97" t="n">
-        <v>2960.916527</v>
+        <v>2958.659121</v>
       </c>
     </row>
     <row r="98">
@@ -7822,58 +7822,58 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>24576.152129</v>
+        <v>24576.653164</v>
       </c>
       <c r="F98" t="n">
-        <v>22344.171413</v>
+        <v>22344.979228</v>
       </c>
       <c r="G98" t="n">
-        <v>22012.024681</v>
+        <v>22013.017785</v>
       </c>
       <c r="H98" t="n">
-        <v>20651.356301</v>
+        <v>20652.390011</v>
       </c>
       <c r="I98" t="n">
-        <v>19530.009574</v>
+        <v>19531.053237</v>
       </c>
       <c r="J98" t="n">
-        <v>19526.387888</v>
+        <v>19527.503948</v>
       </c>
       <c r="K98" t="n">
-        <v>20486.796771</v>
+        <v>20488.067753</v>
       </c>
       <c r="L98" t="n">
-        <v>21797.756016</v>
+        <v>21799.253354</v>
       </c>
       <c r="M98" t="n">
-        <v>22467.62606</v>
+        <v>22469.357204</v>
       </c>
       <c r="N98" t="n">
-        <v>22352.498009</v>
+        <v>22354.440198</v>
       </c>
       <c r="O98" t="n">
-        <v>21962.733022</v>
+        <v>21964.887328</v>
       </c>
       <c r="P98" t="n">
-        <v>21236.667002</v>
+        <v>21239.018135</v>
       </c>
       <c r="Q98" t="n">
-        <v>20405.290898</v>
+        <v>20407.846343</v>
       </c>
       <c r="R98" t="n">
-        <v>19592.373928</v>
+        <v>19595.164858</v>
       </c>
       <c r="S98" t="n">
-        <v>18781.575988</v>
+        <v>18784.634518</v>
       </c>
       <c r="T98" t="n">
-        <v>17946.821603</v>
+        <v>17950.161636</v>
       </c>
       <c r="U98" t="n">
-        <v>17096.014355</v>
+        <v>17099.663441</v>
       </c>
       <c r="V98" t="n">
-        <v>16167.760712</v>
+        <v>16171.748338</v>
       </c>
     </row>
     <row r="99">
@@ -7898,58 +7898,58 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>37509.796017</v>
+        <v>37510.77993</v>
       </c>
       <c r="F99" t="n">
-        <v>39406.354868</v>
+        <v>39408.487474</v>
       </c>
       <c r="G99" t="n">
-        <v>45348.493811</v>
+        <v>45352.204339</v>
       </c>
       <c r="H99" t="n">
-        <v>47843.515209</v>
+        <v>47848.710321</v>
       </c>
       <c r="I99" t="n">
-        <v>48997.373564</v>
+        <v>49003.982944</v>
       </c>
       <c r="J99" t="n">
-        <v>51458.740956</v>
+        <v>51467.054073</v>
       </c>
       <c r="K99" t="n">
-        <v>55517.478153</v>
+        <v>55527.98671</v>
       </c>
       <c r="L99" t="n">
-        <v>59923.640133</v>
+        <v>59936.753183</v>
       </c>
       <c r="M99" t="n">
-        <v>62223.763831</v>
+        <v>62239.362074</v>
       </c>
       <c r="N99" t="n">
-        <v>62204.142852</v>
+        <v>62221.898694</v>
       </c>
       <c r="O99" t="n">
-        <v>61397.437759</v>
+        <v>61417.320639</v>
       </c>
       <c r="P99" t="n">
-        <v>59633.684005</v>
+        <v>59655.571106</v>
       </c>
       <c r="Q99" t="n">
-        <v>57509.246566</v>
+        <v>57533.198693</v>
       </c>
       <c r="R99" t="n">
-        <v>55334.328472</v>
+        <v>55360.557196</v>
       </c>
       <c r="S99" t="n">
-        <v>53078.760442</v>
+        <v>53107.534356</v>
       </c>
       <c r="T99" t="n">
-        <v>50700.526394</v>
+        <v>50732.163024</v>
       </c>
       <c r="U99" t="n">
-        <v>48190.407576</v>
+        <v>48225.356406</v>
       </c>
       <c r="V99" t="n">
-        <v>45254.226795</v>
+        <v>45292.88383</v>
       </c>
     </row>
     <row r="100">
@@ -7974,58 +7974,58 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>7710.057405</v>
+        <v>7709.916302</v>
       </c>
       <c r="F100" t="n">
-        <v>6996.772221</v>
+        <v>6996.467351</v>
       </c>
       <c r="G100" t="n">
-        <v>7018.697957</v>
+        <v>7018.170055</v>
       </c>
       <c r="H100" t="n">
-        <v>6711.092273</v>
+        <v>6710.348116</v>
       </c>
       <c r="I100" t="n">
-        <v>6453.856829</v>
+        <v>6452.89648</v>
       </c>
       <c r="J100" t="n">
-        <v>6539.219758</v>
+        <v>6537.992933</v>
       </c>
       <c r="K100" t="n">
-        <v>6943.390306</v>
+        <v>6941.816988</v>
       </c>
       <c r="L100" t="n">
-        <v>7477.343479</v>
+        <v>7475.356216</v>
       </c>
       <c r="M100" t="n">
-        <v>7817.941271</v>
+        <v>7815.551316</v>
       </c>
       <c r="N100" t="n">
-        <v>7911.161789</v>
+        <v>7908.414436</v>
       </c>
       <c r="O100" t="n">
-        <v>7932.977307</v>
+        <v>7929.871366</v>
       </c>
       <c r="P100" t="n">
-        <v>7852.379752</v>
+        <v>7848.930432</v>
       </c>
       <c r="Q100" t="n">
-        <v>7744.203526</v>
+        <v>7740.398698</v>
       </c>
       <c r="R100" t="n">
-        <v>7652.988742</v>
+        <v>7648.790862</v>
       </c>
       <c r="S100" t="n">
-        <v>7578.910245</v>
+        <v>7574.271631</v>
       </c>
       <c r="T100" t="n">
-        <v>7522.251841</v>
+        <v>7517.107812</v>
       </c>
       <c r="U100" t="n">
-        <v>7492.809848</v>
+        <v>7487.068117</v>
       </c>
       <c r="V100" t="n">
-        <v>7482.485265</v>
+        <v>7476.045439</v>
       </c>
     </row>
     <row r="101">
@@ -8050,58 +8050,58 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>15782.412107</v>
+        <v>15782.753785</v>
       </c>
       <c r="F101" t="n">
-        <v>15259.053798</v>
+        <v>15259.689277</v>
       </c>
       <c r="G101" t="n">
-        <v>16169.006707</v>
+        <v>16169.957647</v>
       </c>
       <c r="H101" t="n">
-        <v>16015.60736</v>
+        <v>16016.791566</v>
       </c>
       <c r="I101" t="n">
-        <v>15666.348073</v>
+        <v>15667.726885</v>
       </c>
       <c r="J101" t="n">
-        <v>15943.447092</v>
+        <v>15945.074533</v>
       </c>
       <c r="K101" t="n">
-        <v>16864.243311</v>
+        <v>16866.213921</v>
       </c>
       <c r="L101" t="n">
-        <v>18008.410038</v>
+        <v>18010.803264</v>
       </c>
       <c r="M101" t="n">
-        <v>18623.013165</v>
+        <v>18625.814536</v>
       </c>
       <c r="N101" t="n">
-        <v>18628.214731</v>
+        <v>18631.378824</v>
       </c>
       <c r="O101" t="n">
-        <v>18466.465368</v>
+        <v>18470.00302</v>
       </c>
       <c r="P101" t="n">
-        <v>18064.68533</v>
+        <v>18068.594064</v>
       </c>
       <c r="Q101" t="n">
-        <v>17582.521495</v>
+        <v>17586.831026</v>
       </c>
       <c r="R101" t="n">
-        <v>17099.38374</v>
+        <v>17104.148364</v>
       </c>
       <c r="S101" t="n">
-        <v>16592.854232</v>
+        <v>16598.12777</v>
       </c>
       <c r="T101" t="n">
-        <v>16053.007582</v>
+        <v>16058.847567</v>
       </c>
       <c r="U101" t="n">
-        <v>15488.268107</v>
+        <v>15494.76356</v>
       </c>
       <c r="V101" t="n">
-        <v>14823.551392</v>
+        <v>14830.789575</v>
       </c>
     </row>
     <row r="102">
@@ -8126,58 +8126,58 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>89335.022495</v>
+        <v>89333.526639</v>
       </c>
       <c r="F102" t="n">
-        <v>91728.75816100001</v>
+        <v>91726.15188200001</v>
       </c>
       <c r="G102" t="n">
-        <v>104223.31085</v>
+        <v>104219.661002</v>
       </c>
       <c r="H102" t="n">
-        <v>110050.498742</v>
+        <v>110046.123343</v>
       </c>
       <c r="I102" t="n">
-        <v>113827.136901</v>
+        <v>113822.081429</v>
       </c>
       <c r="J102" t="n">
-        <v>121220.346484</v>
+        <v>121214.32228</v>
       </c>
       <c r="K102" t="n">
-        <v>132772.683753</v>
+        <v>132765.280555</v>
       </c>
       <c r="L102" t="n">
-        <v>145502.145731</v>
+        <v>145493.040309</v>
       </c>
       <c r="M102" t="n">
-        <v>153365.063729</v>
+        <v>153354.259002</v>
       </c>
       <c r="N102" t="n">
-        <v>155633.083928</v>
+        <v>155620.716744</v>
       </c>
       <c r="O102" t="n">
-        <v>156113.105059</v>
+        <v>156099.099947</v>
       </c>
       <c r="P102" t="n">
-        <v>154413.42339</v>
+        <v>154397.8239</v>
       </c>
       <c r="Q102" t="n">
-        <v>152043.127942</v>
+        <v>152025.883493</v>
       </c>
       <c r="R102" t="n">
-        <v>149822.409753</v>
+        <v>149803.365054</v>
       </c>
       <c r="S102" t="n">
-        <v>147743.378699</v>
+        <v>147722.358447</v>
       </c>
       <c r="T102" t="n">
-        <v>145577.291572</v>
+        <v>145554.135904</v>
       </c>
       <c r="U102" t="n">
-        <v>143428.986101</v>
+        <v>143403.31969</v>
       </c>
       <c r="V102" t="n">
-        <v>140984.890394</v>
+        <v>140956.249674</v>
       </c>
     </row>
     <row r="103">
@@ -8202,58 +8202,58 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>189919.991672</v>
+        <v>189922.558419</v>
       </c>
       <c r="F103" t="n">
-        <v>166591.355189</v>
+        <v>166594.850221</v>
       </c>
       <c r="G103" t="n">
-        <v>159783.267354</v>
+        <v>159786.606775</v>
       </c>
       <c r="H103" t="n">
-        <v>146959.244954</v>
+        <v>146961.689901</v>
       </c>
       <c r="I103" t="n">
-        <v>137068.758859</v>
+        <v>137070.279547</v>
       </c>
       <c r="J103" t="n">
-        <v>135564.890688</v>
+        <v>135565.724608</v>
       </c>
       <c r="K103" t="n">
-        <v>141035.809664</v>
+        <v>141036.219974</v>
       </c>
       <c r="L103" t="n">
-        <v>148974.032542</v>
+        <v>148974.290519</v>
       </c>
       <c r="M103" t="n">
-        <v>152612.930953</v>
+        <v>152613.280155</v>
       </c>
       <c r="N103" t="n">
-        <v>151078.871877</v>
+        <v>151079.441798</v>
       </c>
       <c r="O103" t="n">
-        <v>148012.480189</v>
+        <v>148013.341333</v>
       </c>
       <c r="P103" t="n">
-        <v>143063.063383</v>
+        <v>143064.265579</v>
       </c>
       <c r="Q103" t="n">
-        <v>137714.981086</v>
+        <v>137716.639351</v>
       </c>
       <c r="R103" t="n">
-        <v>132724.76084</v>
+        <v>132727.077129</v>
       </c>
       <c r="S103" t="n">
-        <v>127845.517401</v>
+        <v>127848.641676</v>
       </c>
       <c r="T103" t="n">
-        <v>122924.18173</v>
+        <v>122928.10814</v>
       </c>
       <c r="U103" t="n">
-        <v>118031.688878</v>
+        <v>118036.351133</v>
       </c>
       <c r="V103" t="n">
-        <v>112765.673763</v>
+        <v>112771.289128</v>
       </c>
     </row>
     <row r="104">
@@ -8278,58 +8278,58 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>16587.821879</v>
+        <v>16587.635092</v>
       </c>
       <c r="F104" t="n">
-        <v>16361.244616</v>
+        <v>16360.93294</v>
       </c>
       <c r="G104" t="n">
-        <v>17727.759758</v>
+        <v>17727.327532</v>
       </c>
       <c r="H104" t="n">
-        <v>18160.072133</v>
+        <v>18159.581385</v>
       </c>
       <c r="I104" t="n">
-        <v>18422.500071</v>
+        <v>18421.980756</v>
       </c>
       <c r="J104" t="n">
-        <v>19348.983153</v>
+        <v>19348.42744</v>
       </c>
       <c r="K104" t="n">
-        <v>20907.045406</v>
+        <v>20906.428168</v>
       </c>
       <c r="L104" t="n">
-        <v>22519.329443</v>
+        <v>22518.623979</v>
       </c>
       <c r="M104" t="n">
-        <v>23252.508984</v>
+        <v>23251.712531</v>
       </c>
       <c r="N104" t="n">
-        <v>23064.856694</v>
+        <v>23063.977078</v>
       </c>
       <c r="O104" t="n">
-        <v>22570.880401</v>
+        <v>22569.91851</v>
       </c>
       <c r="P104" t="n">
-        <v>21734.328687</v>
+        <v>21733.289912</v>
       </c>
       <c r="Q104" t="n">
-        <v>20788.884308</v>
+        <v>20787.757652</v>
       </c>
       <c r="R104" t="n">
-        <v>19878.98033</v>
+        <v>19877.741894</v>
       </c>
       <c r="S104" t="n">
-        <v>19026.545151</v>
+        <v>19025.170609</v>
       </c>
       <c r="T104" t="n">
-        <v>18257.347131</v>
+        <v>18255.817125</v>
       </c>
       <c r="U104" t="n">
-        <v>17579.937443</v>
+        <v>17578.247865</v>
       </c>
       <c r="V104" t="n">
-        <v>16899.306882</v>
+        <v>16897.469674</v>
       </c>
     </row>
     <row r="105">
@@ -8354,58 +8354,58 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6698.97693</v>
+        <v>6698.864438</v>
       </c>
       <c r="F105" t="n">
-        <v>6722.726569</v>
+        <v>6722.50278</v>
       </c>
       <c r="G105" t="n">
-        <v>7498.812659</v>
+        <v>7498.458176</v>
       </c>
       <c r="H105" t="n">
-        <v>7773.038988</v>
+        <v>7772.559739</v>
       </c>
       <c r="I105" t="n">
-        <v>7910.18461</v>
+        <v>7909.567612</v>
       </c>
       <c r="J105" t="n">
-        <v>8312.037151</v>
+        <v>8311.230342000001</v>
       </c>
       <c r="K105" t="n">
-        <v>9025.479436</v>
+        <v>9024.411134</v>
       </c>
       <c r="L105" t="n">
-        <v>9841.723378999999</v>
+        <v>9840.332105</v>
       </c>
       <c r="M105" t="n">
-        <v>10356.25185</v>
+        <v>10354.538191</v>
       </c>
       <c r="N105" t="n">
-        <v>10510.497084</v>
+        <v>10508.493639</v>
       </c>
       <c r="O105" t="n">
-        <v>10541.76841</v>
+        <v>10539.477909</v>
       </c>
       <c r="P105" t="n">
-        <v>10406.871376</v>
+        <v>10404.304678</v>
       </c>
       <c r="Q105" t="n">
-        <v>10205.862948</v>
+        <v>10203.005365</v>
       </c>
       <c r="R105" t="n">
-        <v>10004.103061</v>
+        <v>10000.915343</v>
       </c>
       <c r="S105" t="n">
-        <v>9814.328098</v>
+        <v>9810.761047</v>
       </c>
       <c r="T105" t="n">
-        <v>9648.37422</v>
+        <v>9644.368447999999</v>
       </c>
       <c r="U105" t="n">
-        <v>9525.056059</v>
+        <v>9520.540144000001</v>
       </c>
       <c r="V105" t="n">
-        <v>9415.871637</v>
+        <v>9410.774234</v>
       </c>
     </row>
     <row r="106">
@@ -8430,58 +8430,58 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>74743.097012</v>
+        <v>74741.282997</v>
       </c>
       <c r="F106" t="n">
-        <v>77388.684458</v>
+        <v>77385.653814</v>
       </c>
       <c r="G106" t="n">
-        <v>89375.994699</v>
+        <v>89372.046263</v>
       </c>
       <c r="H106" t="n">
-        <v>95051.088267</v>
+        <v>95046.715071</v>
       </c>
       <c r="I106" t="n">
-        <v>98222.05821800001</v>
+        <v>98217.381032</v>
       </c>
       <c r="J106" t="n">
-        <v>103876.902547</v>
+        <v>103871.682437</v>
       </c>
       <c r="K106" t="n">
-        <v>112454.420777</v>
+        <v>112448.32411</v>
       </c>
       <c r="L106" t="n">
-        <v>121279.820767</v>
+        <v>121272.591778</v>
       </c>
       <c r="M106" t="n">
-        <v>125554.353421</v>
+        <v>125546.088882</v>
       </c>
       <c r="N106" t="n">
-        <v>124948.52947</v>
+        <v>124939.445979</v>
       </c>
       <c r="O106" t="n">
-        <v>122700.358882</v>
+        <v>122690.506333</v>
       </c>
       <c r="P106" t="n">
-        <v>118601.341353</v>
+        <v>118590.767121</v>
       </c>
       <c r="Q106" t="n">
-        <v>114031.284886</v>
+        <v>114019.904767</v>
       </c>
       <c r="R106" t="n">
-        <v>109798.595036</v>
+        <v>109786.24056</v>
       </c>
       <c r="S106" t="n">
-        <v>106031.221071</v>
+        <v>106017.770008</v>
       </c>
       <c r="T106" t="n">
-        <v>102665.269586</v>
+        <v>102650.722418</v>
       </c>
       <c r="U106" t="n">
-        <v>99595.73900099999</v>
+        <v>99580.11926599999</v>
       </c>
       <c r="V106" t="n">
-        <v>96384.323984</v>
+        <v>96367.520307</v>
       </c>
     </row>
     <row r="107">
@@ -8506,58 +8506,58 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>1624.904923</v>
+        <v>1624.920374</v>
       </c>
       <c r="F107" t="n">
-        <v>1765.729009</v>
+        <v>1765.768218</v>
       </c>
       <c r="G107" t="n">
-        <v>1992.702372</v>
+        <v>1992.765529</v>
       </c>
       <c r="H107" t="n">
-        <v>2075.523471</v>
+        <v>2075.60351</v>
       </c>
       <c r="I107" t="n">
-        <v>2136.173711</v>
+        <v>2136.268602</v>
       </c>
       <c r="J107" t="n">
-        <v>2289.648597</v>
+        <v>2289.764327</v>
       </c>
       <c r="K107" t="n">
-        <v>2544.004614</v>
+        <v>2544.150634</v>
       </c>
       <c r="L107" t="n">
-        <v>2837.592446</v>
+        <v>2837.777011</v>
       </c>
       <c r="M107" t="n">
-        <v>3042.884012</v>
+        <v>3043.106573</v>
       </c>
       <c r="N107" t="n">
-        <v>3130.960539</v>
+        <v>3131.215201</v>
       </c>
       <c r="O107" t="n">
-        <v>3167.906141</v>
+        <v>3168.190475</v>
       </c>
       <c r="P107" t="n">
-        <v>3141.839993</v>
+        <v>3142.149755</v>
       </c>
       <c r="Q107" t="n">
-        <v>3083.452252</v>
+        <v>3083.785492</v>
       </c>
       <c r="R107" t="n">
-        <v>3012.001193</v>
+        <v>3012.357708</v>
       </c>
       <c r="S107" t="n">
-        <v>2928.875636</v>
+        <v>2929.255176</v>
       </c>
       <c r="T107" t="n">
-        <v>2835.054529</v>
+        <v>2835.455575</v>
       </c>
       <c r="U107" t="n">
-        <v>2734.560791</v>
+        <v>2734.983565</v>
       </c>
       <c r="V107" t="n">
-        <v>2617.014117</v>
+        <v>2617.458451</v>
       </c>
     </row>
     <row r="108">
@@ -8582,58 +8582,58 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>50679.106926</v>
+        <v>50680.140083</v>
       </c>
       <c r="F108" t="n">
-        <v>49678.53771</v>
+        <v>49680.524123</v>
       </c>
       <c r="G108" t="n">
-        <v>52592.281936</v>
+        <v>52595.246604</v>
       </c>
       <c r="H108" t="n">
-        <v>52023.902101</v>
+        <v>52027.572167</v>
       </c>
       <c r="I108" t="n">
-        <v>50910.759055</v>
+        <v>50915.02223</v>
       </c>
       <c r="J108" t="n">
-        <v>51886.08448</v>
+        <v>51891.123979</v>
       </c>
       <c r="K108" t="n">
-        <v>54910.615758</v>
+        <v>54916.72968</v>
       </c>
       <c r="L108" t="n">
-        <v>58608.489874</v>
+        <v>58615.931568</v>
       </c>
       <c r="M108" t="n">
-        <v>60518.503807</v>
+        <v>60527.227335</v>
       </c>
       <c r="N108" t="n">
-        <v>60395.531969</v>
+        <v>60405.379566</v>
       </c>
       <c r="O108" t="n">
-        <v>59710.889072</v>
+        <v>59721.869402</v>
       </c>
       <c r="P108" t="n">
-        <v>58285.444724</v>
+        <v>58297.536642</v>
       </c>
       <c r="Q108" t="n">
-        <v>56679.185645</v>
+        <v>56692.487337</v>
       </c>
       <c r="R108" t="n">
-        <v>55180.795903</v>
+        <v>55195.516484</v>
       </c>
       <c r="S108" t="n">
-        <v>53733.327787</v>
+        <v>53749.727989</v>
       </c>
       <c r="T108" t="n">
-        <v>52236.624342</v>
+        <v>52254.967543</v>
       </c>
       <c r="U108" t="n">
-        <v>50638.628894</v>
+        <v>50659.205509</v>
       </c>
       <c r="V108" t="n">
-        <v>48658.17821</v>
+        <v>48681.258556</v>
       </c>
     </row>
     <row r="109">
@@ -8658,58 +8658,58 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>13930.847749</v>
+        <v>13930.677646</v>
       </c>
       <c r="F109" t="n">
-        <v>13749.88137</v>
+        <v>13749.580891</v>
       </c>
       <c r="G109" t="n">
-        <v>15590.079336</v>
+        <v>15589.709244</v>
       </c>
       <c r="H109" t="n">
-        <v>16918.4782</v>
+        <v>16918.167542</v>
       </c>
       <c r="I109" t="n">
-        <v>18237.481964</v>
+        <v>18237.339265</v>
       </c>
       <c r="J109" t="n">
-        <v>20138.006136</v>
+        <v>20138.094193</v>
       </c>
       <c r="K109" t="n">
-        <v>22605.599542</v>
+        <v>22605.969334</v>
       </c>
       <c r="L109" t="n">
-        <v>25072.821967</v>
+        <v>25073.507465</v>
       </c>
       <c r="M109" t="n">
-        <v>26479.356986</v>
+        <v>26480.343773</v>
       </c>
       <c r="N109" t="n">
-        <v>26734.710574</v>
+        <v>26735.952816</v>
       </c>
       <c r="O109" t="n">
-        <v>26535.314656</v>
+        <v>26536.787654</v>
       </c>
       <c r="P109" t="n">
-        <v>25847.665564</v>
+        <v>25849.342004</v>
       </c>
       <c r="Q109" t="n">
-        <v>24963.43652</v>
+        <v>24965.302575</v>
       </c>
       <c r="R109" t="n">
-        <v>24062.053331</v>
+        <v>24064.102776</v>
       </c>
       <c r="S109" t="n">
-        <v>23184.651914</v>
+        <v>23186.892852</v>
       </c>
       <c r="T109" t="n">
-        <v>22355.235516</v>
+        <v>22357.695273</v>
       </c>
       <c r="U109" t="n">
-        <v>21586.797893</v>
+        <v>21589.531286</v>
       </c>
       <c r="V109" t="n">
-        <v>20760.13728</v>
+        <v>20763.200733</v>
       </c>
     </row>
     <row r="110">
@@ -8734,58 +8734,58 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>16773.175421</v>
+        <v>16773.094283</v>
       </c>
       <c r="F110" t="n">
-        <v>17563.026036</v>
+        <v>17562.935639</v>
       </c>
       <c r="G110" t="n">
-        <v>20289.000773</v>
+        <v>20288.966942</v>
       </c>
       <c r="H110" t="n">
-        <v>21507.406362</v>
+        <v>21507.448967</v>
       </c>
       <c r="I110" t="n">
-        <v>22102.650503</v>
+        <v>22102.739072</v>
       </c>
       <c r="J110" t="n">
-        <v>23349.054437</v>
+        <v>23349.157443</v>
       </c>
       <c r="K110" t="n">
-        <v>25443.755505</v>
+        <v>25443.84593</v>
       </c>
       <c r="L110" t="n">
-        <v>27858.417506</v>
+        <v>27858.475253</v>
       </c>
       <c r="M110" t="n">
-        <v>29441.531289</v>
+        <v>29441.54174</v>
       </c>
       <c r="N110" t="n">
-        <v>30024.657848</v>
+        <v>30024.623226</v>
       </c>
       <c r="O110" t="n">
-        <v>30269.140985</v>
+        <v>30269.072207</v>
       </c>
       <c r="P110" t="n">
-        <v>30057.600983</v>
+        <v>30057.507458</v>
       </c>
       <c r="Q110" t="n">
-        <v>29663.18314</v>
+        <v>29663.069025</v>
       </c>
       <c r="R110" t="n">
-        <v>29233.332855</v>
+        <v>29233.194495</v>
       </c>
       <c r="S110" t="n">
-        <v>28748.86648</v>
+        <v>28748.694576</v>
       </c>
       <c r="T110" t="n">
-        <v>28199.015354</v>
+        <v>28198.781794</v>
       </c>
       <c r="U110" t="n">
-        <v>27606.716884</v>
+        <v>27606.381269</v>
       </c>
       <c r="V110" t="n">
-        <v>26887.371508</v>
+        <v>26886.910301</v>
       </c>
     </row>
     <row r="111">
@@ -8810,58 +8810,58 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>78674.739145</v>
+        <v>78674.489028</v>
       </c>
       <c r="F111" t="n">
-        <v>79787.75081699999</v>
+        <v>79787.49933599999</v>
       </c>
       <c r="G111" t="n">
-        <v>88069.44902</v>
+        <v>88069.287687</v>
       </c>
       <c r="H111" t="n">
-        <v>90289.979202</v>
+        <v>90289.9078</v>
       </c>
       <c r="I111" t="n">
-        <v>91413.445406</v>
+        <v>91413.453251</v>
       </c>
       <c r="J111" t="n">
-        <v>95965.96915</v>
+        <v>95966.041471</v>
       </c>
       <c r="K111" t="n">
-        <v>103839.01245</v>
+        <v>103839.099779</v>
       </c>
       <c r="L111" t="n">
-        <v>112151.404288</v>
+        <v>112151.393986</v>
       </c>
       <c r="M111" t="n">
-        <v>116374.19687</v>
+        <v>116374.019414</v>
       </c>
       <c r="N111" t="n">
-        <v>116186.794265</v>
+        <v>116186.43664</v>
       </c>
       <c r="O111" t="n">
-        <v>114527.230193</v>
+        <v>114526.713101</v>
       </c>
       <c r="P111" t="n">
-        <v>111046.930437</v>
+        <v>111046.215596</v>
       </c>
       <c r="Q111" t="n">
-        <v>106855.425431</v>
+        <v>106854.384314</v>
       </c>
       <c r="R111" t="n">
-        <v>102627.413099</v>
+        <v>102625.834184</v>
       </c>
       <c r="S111" t="n">
-        <v>98545.40961</v>
+        <v>98543.06501200001</v>
       </c>
       <c r="T111" t="n">
-        <v>94810.72494</v>
+        <v>94807.559186</v>
       </c>
       <c r="U111" t="n">
-        <v>91526.685958</v>
+        <v>91522.816139</v>
       </c>
       <c r="V111" t="n">
-        <v>88242.828288</v>
+        <v>88238.305498</v>
       </c>
     </row>
     <row r="112">
@@ -8886,58 +8886,58 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>96638.236011</v>
+        <v>96637.045643</v>
       </c>
       <c r="F112" t="n">
-        <v>99556.890228</v>
+        <v>99554.913287</v>
       </c>
       <c r="G112" t="n">
-        <v>113742.481479</v>
+        <v>113739.937811</v>
       </c>
       <c r="H112" t="n">
-        <v>120299.790999</v>
+        <v>120296.985123</v>
       </c>
       <c r="I112" t="n">
-        <v>124286.112957</v>
+        <v>124283.077953</v>
       </c>
       <c r="J112" t="n">
-        <v>132066.005799</v>
+        <v>132062.530309</v>
       </c>
       <c r="K112" t="n">
-        <v>144406.878737</v>
+        <v>144402.669514</v>
       </c>
       <c r="L112" t="n">
-        <v>157983.441693</v>
+        <v>157978.239312</v>
       </c>
       <c r="M112" t="n">
-        <v>166151.58333</v>
+        <v>166145.306832</v>
       </c>
       <c r="N112" t="n">
-        <v>168154.660691</v>
+        <v>168147.357483</v>
       </c>
       <c r="O112" t="n">
-        <v>168174.296464</v>
+        <v>168165.924684</v>
       </c>
       <c r="P112" t="n">
-        <v>165856.154814</v>
+        <v>165846.764411</v>
       </c>
       <c r="Q112" t="n">
-        <v>162863.280626</v>
+        <v>162852.873137</v>
       </c>
       <c r="R112" t="n">
-        <v>160049.5109</v>
+        <v>160038.024274</v>
       </c>
       <c r="S112" t="n">
-        <v>157306.246939</v>
+        <v>157293.564025</v>
       </c>
       <c r="T112" t="n">
-        <v>154548.313472</v>
+        <v>154534.148365</v>
       </c>
       <c r="U112" t="n">
-        <v>151964.124291</v>
+        <v>151948.074691</v>
       </c>
       <c r="V112" t="n">
-        <v>149178.92396</v>
+        <v>149160.640451</v>
       </c>
     </row>
     <row r="113">
@@ -8962,58 +8962,58 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>16315.313519</v>
+        <v>16303.985247</v>
       </c>
       <c r="F113" t="n">
-        <v>16621.897114</v>
+        <v>16594.374223</v>
       </c>
       <c r="G113" t="n">
-        <v>14237.986132</v>
+        <v>14191.599417</v>
       </c>
       <c r="H113" t="n">
-        <v>13283.765067</v>
+        <v>13215.934005</v>
       </c>
       <c r="I113" t="n">
-        <v>12712.481976</v>
+        <v>12623.632098</v>
       </c>
       <c r="J113" t="n">
-        <v>12540.785263</v>
+        <v>12430.877423</v>
       </c>
       <c r="K113" t="n">
-        <v>12436.878751</v>
+        <v>12307.384548</v>
       </c>
       <c r="L113" t="n">
-        <v>12296.587537</v>
+        <v>12149.177753</v>
       </c>
       <c r="M113" t="n">
-        <v>12180.946331</v>
+        <v>12015.727565</v>
       </c>
       <c r="N113" t="n">
-        <v>11994.491277</v>
+        <v>11812.520918</v>
       </c>
       <c r="O113" t="n">
-        <v>11708.548406</v>
+        <v>11511.561778</v>
       </c>
       <c r="P113" t="n">
-        <v>11390.600274</v>
+        <v>11179.608593</v>
       </c>
       <c r="Q113" t="n">
-        <v>11063.994052</v>
+        <v>10839.88093</v>
       </c>
       <c r="R113" t="n">
-        <v>10766.275837</v>
+        <v>10529.184261</v>
       </c>
       <c r="S113" t="n">
-        <v>10507.139738</v>
+        <v>10256.963703</v>
       </c>
       <c r="T113" t="n">
-        <v>10290.366623</v>
+        <v>10026.949995</v>
       </c>
       <c r="U113" t="n">
-        <v>10112.467117</v>
+        <v>9836.339980999999</v>
       </c>
       <c r="V113" t="n">
-        <v>9994.780183999999</v>
+        <v>9707.539041</v>
       </c>
     </row>
     <row r="114">
@@ -9038,58 +9038,58 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>1662.52615</v>
+        <v>1652.997864</v>
       </c>
       <c r="F114" t="n">
-        <v>2396.382523</v>
+        <v>2380.069783</v>
       </c>
       <c r="G114" t="n">
-        <v>3017.345457</v>
+        <v>2998.279145</v>
       </c>
       <c r="H114" t="n">
-        <v>3627.205399</v>
+        <v>3605.039451</v>
       </c>
       <c r="I114" t="n">
-        <v>3933.77805</v>
+        <v>3908.6543</v>
       </c>
       <c r="J114" t="n">
-        <v>4009.534391</v>
+        <v>3981.21875</v>
       </c>
       <c r="K114" t="n">
-        <v>3903.166185</v>
+        <v>3871.9273</v>
       </c>
       <c r="L114" t="n">
-        <v>3695.460904</v>
+        <v>3661.676888</v>
       </c>
       <c r="M114" t="n">
-        <v>3478.778909</v>
+        <v>3442.607366</v>
       </c>
       <c r="N114" t="n">
-        <v>3248.886013</v>
+        <v>3210.790883</v>
       </c>
       <c r="O114" t="n">
-        <v>3016.996736</v>
+        <v>2977.456984</v>
       </c>
       <c r="P114" t="n">
-        <v>2801.724979</v>
+        <v>2761.124505</v>
       </c>
       <c r="Q114" t="n">
-        <v>2602.631767</v>
+        <v>2561.316236</v>
       </c>
       <c r="R114" t="n">
-        <v>2424.865877</v>
+        <v>2382.934275</v>
       </c>
       <c r="S114" t="n">
-        <v>2270.10251</v>
+        <v>2227.497154</v>
       </c>
       <c r="T114" t="n">
-        <v>2139.647022</v>
+        <v>2096.224432</v>
       </c>
       <c r="U114" t="n">
-        <v>2032.364827</v>
+        <v>1988.027785</v>
       </c>
       <c r="V114" t="n">
-        <v>1950.762735</v>
+        <v>1905.575212</v>
       </c>
     </row>
     <row r="115">
@@ -9114,58 +9114,58 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>90405.740727</v>
+        <v>90426.597286</v>
       </c>
       <c r="F115" t="n">
-        <v>105020.148375</v>
+        <v>105063.984006</v>
       </c>
       <c r="G115" t="n">
-        <v>111136.41765</v>
+        <v>111201.870677</v>
       </c>
       <c r="H115" t="n">
-        <v>120849.762129</v>
+        <v>120939.759139</v>
       </c>
       <c r="I115" t="n">
-        <v>126150.184027</v>
+        <v>126264.157654</v>
       </c>
       <c r="J115" t="n">
-        <v>129012.606696</v>
+        <v>129150.830176</v>
       </c>
       <c r="K115" t="n">
-        <v>128934.617937</v>
+        <v>129095.351024</v>
       </c>
       <c r="L115" t="n">
-        <v>126894.079476</v>
+        <v>127075.273276</v>
       </c>
       <c r="M115" t="n">
-        <v>124862.864116</v>
+        <v>125064.254424</v>
       </c>
       <c r="N115" t="n">
-        <v>122361.526683</v>
+        <v>122581.592173</v>
       </c>
       <c r="O115" t="n">
-        <v>118998.714566</v>
+        <v>119235.240945</v>
       </c>
       <c r="P115" t="n">
-        <v>115306.460595</v>
+        <v>115558.052751</v>
       </c>
       <c r="Q115" t="n">
-        <v>111312.630343</v>
+        <v>111578.058996</v>
       </c>
       <c r="R115" t="n">
-        <v>107262.501628</v>
+        <v>107541.524806</v>
       </c>
       <c r="S115" t="n">
-        <v>103117.28818</v>
+        <v>103410.069571</v>
       </c>
       <c r="T115" t="n">
-        <v>98764.058832</v>
+        <v>99070.898049</v>
       </c>
       <c r="U115" t="n">
-        <v>93999.98843700001</v>
+        <v>94320.452616</v>
       </c>
       <c r="V115" t="n">
-        <v>88818.80392000001</v>
+        <v>89151.23258500001</v>
       </c>
     </row>
     <row r="116">
@@ -9190,58 +9190,58 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>1868.175445</v>
+        <v>1868.190032</v>
       </c>
       <c r="F116" t="n">
-        <v>1986.846286</v>
+        <v>1986.875242</v>
       </c>
       <c r="G116" t="n">
-        <v>2107.356347</v>
+        <v>2107.399877</v>
       </c>
       <c r="H116" t="n">
-        <v>2186.067996</v>
+        <v>2186.126233</v>
       </c>
       <c r="I116" t="n">
-        <v>2228.102211</v>
+        <v>2228.175286</v>
       </c>
       <c r="J116" t="n">
-        <v>2273.937942</v>
+        <v>2274.027059</v>
       </c>
       <c r="K116" t="n">
-        <v>2341.939881</v>
+        <v>2342.047124</v>
       </c>
       <c r="L116" t="n">
-        <v>2415.608478</v>
+        <v>2415.735513</v>
       </c>
       <c r="M116" t="n">
-        <v>2450.131941</v>
+        <v>2450.27777</v>
       </c>
       <c r="N116" t="n">
-        <v>2428.275464</v>
+        <v>2428.437041</v>
       </c>
       <c r="O116" t="n">
-        <v>2374.103526</v>
+        <v>2374.278457</v>
       </c>
       <c r="P116" t="n">
-        <v>2290.721829</v>
+        <v>2290.907412</v>
       </c>
       <c r="Q116" t="n">
-        <v>2193.024958</v>
+        <v>2193.219267</v>
       </c>
       <c r="R116" t="n">
-        <v>2092.020638</v>
+        <v>2092.222475</v>
       </c>
       <c r="S116" t="n">
-        <v>1989.994659</v>
+        <v>1990.202993</v>
       </c>
       <c r="T116" t="n">
-        <v>1890.075753</v>
+        <v>1890.289818</v>
       </c>
       <c r="U116" t="n">
-        <v>1792.539228</v>
+        <v>1792.75831</v>
       </c>
       <c r="V116" t="n">
-        <v>1695.491456</v>
+        <v>1695.714725</v>
       </c>
     </row>
     <row r="117">
@@ -9266,58 +9266,58 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>4706.448198</v>
+        <v>4706.451179</v>
       </c>
       <c r="F117" t="n">
-        <v>6167.582135</v>
+        <v>6167.567356</v>
       </c>
       <c r="G117" t="n">
-        <v>7196.886363</v>
+        <v>7196.843506</v>
       </c>
       <c r="H117" t="n">
-        <v>7829.609585</v>
+        <v>7829.535147</v>
       </c>
       <c r="I117" t="n">
-        <v>8142.016416</v>
+        <v>8141.912118</v>
       </c>
       <c r="J117" t="n">
-        <v>8340.704285</v>
+        <v>8340.572136000001</v>
       </c>
       <c r="K117" t="n">
-        <v>8543.183362</v>
+        <v>8543.023972000001</v>
       </c>
       <c r="L117" t="n">
-        <v>8721.450285999999</v>
+        <v>8721.263783</v>
       </c>
       <c r="M117" t="n">
-        <v>8710.516953</v>
+        <v>8710.307887000001</v>
       </c>
       <c r="N117" t="n">
-        <v>8470.662004</v>
+        <v>8470.437232</v>
       </c>
       <c r="O117" t="n">
-        <v>8136.193813</v>
+        <v>8135.956454</v>
       </c>
       <c r="P117" t="n">
-        <v>7745.007623</v>
+        <v>7744.759366</v>
       </c>
       <c r="Q117" t="n">
-        <v>7362.81065</v>
+        <v>7362.550091</v>
       </c>
       <c r="R117" t="n">
-        <v>7016.500357</v>
+        <v>7016.225428</v>
       </c>
       <c r="S117" t="n">
-        <v>6700.076135</v>
+        <v>6699.785394</v>
       </c>
       <c r="T117" t="n">
-        <v>6406.570793</v>
+        <v>6406.264355</v>
       </c>
       <c r="U117" t="n">
-        <v>6125.943718</v>
+        <v>6125.62275</v>
       </c>
       <c r="V117" t="n">
-        <v>5853.301073</v>
+        <v>5852.96583</v>
       </c>
     </row>
     <row r="118">
@@ -9342,58 +9342,58 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6491.510964</v>
+        <v>6491.517915</v>
       </c>
       <c r="F118" t="n">
-        <v>6734.202703</v>
+        <v>6734.215098</v>
       </c>
       <c r="G118" t="n">
-        <v>6925.930032</v>
+        <v>6925.948382</v>
       </c>
       <c r="H118" t="n">
-        <v>7002.861584</v>
+        <v>7002.88696</v>
       </c>
       <c r="I118" t="n">
-        <v>7002.69937</v>
+        <v>7002.733082</v>
       </c>
       <c r="J118" t="n">
-        <v>7040.926486</v>
+        <v>7040.970538</v>
       </c>
       <c r="K118" t="n">
-        <v>7164.697472</v>
+        <v>7164.754331</v>
       </c>
       <c r="L118" t="n">
-        <v>7315.451181</v>
+        <v>7315.52315</v>
       </c>
       <c r="M118" t="n">
-        <v>7354.152455</v>
+        <v>7354.240295</v>
       </c>
       <c r="N118" t="n">
-        <v>7244.788413</v>
+        <v>7244.890602</v>
       </c>
       <c r="O118" t="n">
-        <v>7080.329421</v>
+        <v>7080.442984</v>
       </c>
       <c r="P118" t="n">
-        <v>6868.20677</v>
+        <v>6868.328485</v>
       </c>
       <c r="Q118" t="n">
-        <v>6656.031662</v>
+        <v>6656.158015</v>
       </c>
       <c r="R118" t="n">
-        <v>6465.550321</v>
+        <v>6465.678442</v>
       </c>
       <c r="S118" t="n">
-        <v>6290.327043</v>
+        <v>6290.454597</v>
       </c>
       <c r="T118" t="n">
-        <v>6120.3855</v>
+        <v>6120.511245</v>
       </c>
       <c r="U118" t="n">
-        <v>5943.04222</v>
+        <v>5943.165624</v>
       </c>
       <c r="V118" t="n">
-        <v>5747.361156</v>
+        <v>5747.481468</v>
       </c>
     </row>
     <row r="119">
@@ -9418,58 +9418,58 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>1981.094383</v>
+        <v>1981.103242</v>
       </c>
       <c r="F119" t="n">
-        <v>2480.989984</v>
+        <v>2481.002804</v>
       </c>
       <c r="G119" t="n">
-        <v>3032.207009</v>
+        <v>3032.218278</v>
       </c>
       <c r="H119" t="n">
-        <v>3503.033303</v>
+        <v>3503.039122</v>
       </c>
       <c r="I119" t="n">
-        <v>3851.536583</v>
+        <v>3851.535911</v>
       </c>
       <c r="J119" t="n">
-        <v>4144.740107</v>
+        <v>4144.733732</v>
       </c>
       <c r="K119" t="n">
-        <v>4434.713583</v>
+        <v>4434.703027</v>
       </c>
       <c r="L119" t="n">
-        <v>4713.854269</v>
+        <v>4713.84082</v>
       </c>
       <c r="M119" t="n">
-        <v>4902.342604</v>
+        <v>4902.327526</v>
       </c>
       <c r="N119" t="n">
-        <v>4970.934025</v>
+        <v>4970.917991</v>
       </c>
       <c r="O119" t="n">
-        <v>4971.323866</v>
+        <v>4971.30595</v>
       </c>
       <c r="P119" t="n">
-        <v>4905.566732</v>
+        <v>4905.546348</v>
       </c>
       <c r="Q119" t="n">
-        <v>4809.581589</v>
+        <v>4809.557697</v>
       </c>
       <c r="R119" t="n">
-        <v>4707.911532</v>
+        <v>4707.882756</v>
       </c>
       <c r="S119" t="n">
-        <v>4602.548851</v>
+        <v>4602.513745</v>
       </c>
       <c r="T119" t="n">
-        <v>4489.40159</v>
+        <v>4489.359373</v>
       </c>
       <c r="U119" t="n">
-        <v>4359.661514</v>
+        <v>4359.612258</v>
       </c>
       <c r="V119" t="n">
-        <v>4205.534449</v>
+        <v>4205.478299</v>
       </c>
     </row>
     <row r="120">
@@ -9494,58 +9494,58 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>2.478804</v>
+        <v>2.489316</v>
       </c>
       <c r="F120" t="n">
-        <v>5.071565</v>
+        <v>5.093015</v>
       </c>
       <c r="G120" t="n">
-        <v>7.845969</v>
+        <v>7.879067</v>
       </c>
       <c r="H120" t="n">
-        <v>10.741317</v>
+        <v>10.786513</v>
       </c>
       <c r="I120" t="n">
-        <v>13.708227</v>
+        <v>13.765758</v>
       </c>
       <c r="J120" t="n">
-        <v>16.945184</v>
+        <v>17.016117</v>
       </c>
       <c r="K120" t="n">
-        <v>20.645221</v>
+        <v>20.731419</v>
       </c>
       <c r="L120" t="n">
-        <v>24.786886</v>
+        <v>24.890105</v>
       </c>
       <c r="M120" t="n">
-        <v>28.906297</v>
+        <v>29.026346</v>
       </c>
       <c r="N120" t="n">
-        <v>32.613454</v>
+        <v>32.748526</v>
       </c>
       <c r="O120" t="n">
-        <v>35.94089</v>
+        <v>36.08932</v>
       </c>
       <c r="P120" t="n">
-        <v>38.793248</v>
+        <v>38.952986</v>
       </c>
       <c r="Q120" t="n">
-        <v>41.333249</v>
+        <v>41.502924</v>
       </c>
       <c r="R120" t="n">
-        <v>43.712888</v>
+        <v>43.891755</v>
       </c>
       <c r="S120" t="n">
-        <v>45.953995</v>
+        <v>46.141395</v>
       </c>
       <c r="T120" t="n">
-        <v>48.041475</v>
+        <v>48.236691</v>
       </c>
       <c r="U120" t="n">
-        <v>49.896607</v>
+        <v>50.098609</v>
       </c>
       <c r="V120" t="n">
-        <v>51.40476</v>
+        <v>51.612055</v>
       </c>
     </row>
     <row r="121">
@@ -9570,58 +9570,58 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>37.353022</v>
+        <v>37.511428</v>
       </c>
       <c r="F121" t="n">
-        <v>79.395129</v>
+        <v>79.730921</v>
       </c>
       <c r="G121" t="n">
-        <v>126.832769</v>
+        <v>127.36781</v>
       </c>
       <c r="H121" t="n">
-        <v>176.83148</v>
+        <v>177.575526</v>
       </c>
       <c r="I121" t="n">
-        <v>226.855148</v>
+        <v>227.807226</v>
       </c>
       <c r="J121" t="n">
-        <v>279.573812</v>
+        <v>280.744119</v>
       </c>
       <c r="K121" t="n">
-        <v>337.991657</v>
+        <v>339.402846</v>
       </c>
       <c r="L121" t="n">
-        <v>401.953259</v>
+        <v>403.627092</v>
       </c>
       <c r="M121" t="n">
-        <v>464.393838</v>
+        <v>466.322494</v>
       </c>
       <c r="N121" t="n">
-        <v>519.383333</v>
+        <v>521.534409</v>
       </c>
       <c r="O121" t="n">
-        <v>568.392638</v>
+        <v>570.739994</v>
       </c>
       <c r="P121" t="n">
-        <v>609.914582</v>
+        <v>612.426017</v>
       </c>
       <c r="Q121" t="n">
-        <v>647.169678</v>
+        <v>649.826341</v>
       </c>
       <c r="R121" t="n">
-        <v>682.853298</v>
+        <v>685.647429</v>
       </c>
       <c r="S121" t="n">
-        <v>717.48855</v>
+        <v>720.414456</v>
       </c>
       <c r="T121" t="n">
-        <v>750.545834</v>
+        <v>753.595671</v>
       </c>
       <c r="U121" t="n">
-        <v>780.104244</v>
+        <v>783.262435</v>
       </c>
       <c r="V121" t="n">
-        <v>804.375972</v>
+        <v>807.6197100000001</v>
       </c>
     </row>
     <row r="122">
@@ -9646,58 +9646,58 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>121095.686333</v>
+        <v>121095.484037</v>
       </c>
       <c r="F122" t="n">
-        <v>129866.106169</v>
+        <v>129865.709534</v>
       </c>
       <c r="G122" t="n">
-        <v>139617.659748</v>
+        <v>139617.061316</v>
       </c>
       <c r="H122" t="n">
-        <v>147771.437616</v>
+        <v>147770.633381</v>
       </c>
       <c r="I122" t="n">
-        <v>154593.276488</v>
+        <v>154592.265061</v>
       </c>
       <c r="J122" t="n">
-        <v>162445.082224</v>
+        <v>162443.846338</v>
       </c>
       <c r="K122" t="n">
-        <v>172434.542394</v>
+        <v>172433.050851</v>
       </c>
       <c r="L122" t="n">
-        <v>183138.706538</v>
+        <v>183136.930432</v>
       </c>
       <c r="M122" t="n">
-        <v>190906.799079</v>
+        <v>190904.74085</v>
       </c>
       <c r="N122" t="n">
-        <v>194002.616774</v>
+        <v>194000.307665</v>
       </c>
       <c r="O122" t="n">
-        <v>194438.055127</v>
+        <v>194435.526122</v>
       </c>
       <c r="P122" t="n">
-        <v>192559.977673</v>
+        <v>192557.26784</v>
       </c>
       <c r="Q122" t="n">
-        <v>189614.655743</v>
+        <v>189611.793195</v>
       </c>
       <c r="R122" t="n">
-        <v>186515.24974</v>
+        <v>186512.25049</v>
       </c>
       <c r="S122" t="n">
-        <v>183372.911991</v>
+        <v>183369.788644</v>
       </c>
       <c r="T122" t="n">
-        <v>180271.013395</v>
+        <v>180267.777187</v>
       </c>
       <c r="U122" t="n">
-        <v>177079.247195</v>
+        <v>177075.91474</v>
       </c>
       <c r="V122" t="n">
-        <v>173404.037135</v>
+        <v>173400.633913</v>
       </c>
     </row>
     <row r="123">
@@ -9722,19 +9722,19 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>1681.428887</v>
+        <v>1681.531645</v>
       </c>
       <c r="F123" t="n">
-        <v>1712.197168</v>
+        <v>1712.423123</v>
       </c>
       <c r="G123" t="n">
-        <v>1869.190303</v>
+        <v>1869.609608</v>
       </c>
       <c r="H123" t="n">
-        <v>1855.460609</v>
+        <v>1856.139035</v>
       </c>
       <c r="I123" t="n">
-        <v>1668.832826</v>
+        <v>1669.872099</v>
       </c>
       <c r="J123" t="n">
         <v>961.383724</v>
@@ -9798,19 +9798,19 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>22670.697778</v>
+        <v>22671.855133</v>
       </c>
       <c r="F124" t="n">
-        <v>23229.787278</v>
+        <v>23232.362826</v>
       </c>
       <c r="G124" t="n">
-        <v>25180.65881</v>
+        <v>25185.363637</v>
       </c>
       <c r="H124" t="n">
-        <v>25007.474173</v>
+        <v>25015.002886</v>
       </c>
       <c r="I124" t="n">
-        <v>22705.859712</v>
+        <v>22717.20976</v>
       </c>
       <c r="J124" t="n">
         <v>15045.318803</v>
@@ -9874,19 +9874,19 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6427.523637</v>
+        <v>6426.263523</v>
       </c>
       <c r="F125" t="n">
-        <v>6585.1202</v>
+        <v>6582.318696</v>
       </c>
       <c r="G125" t="n">
-        <v>7286.733995</v>
+        <v>7281.609862</v>
       </c>
       <c r="H125" t="n">
-        <v>8031.784905</v>
+        <v>8023.577766</v>
       </c>
       <c r="I125" t="n">
-        <v>9660.378116</v>
+        <v>9647.988794999999</v>
       </c>
       <c r="J125" t="n">
         <v>18553.878108</v>
@@ -10254,58 +10254,58 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>81518.81346200001</v>
+        <v>81550.95167900001</v>
       </c>
       <c r="F130" t="n">
-        <v>93709.37968500001</v>
+        <v>93784.66256300001</v>
       </c>
       <c r="G130" t="n">
-        <v>112262.612988</v>
+        <v>112403.178873</v>
       </c>
       <c r="H130" t="n">
-        <v>128668.206435</v>
+        <v>128889.900207</v>
       </c>
       <c r="I130" t="n">
-        <v>144150.154587</v>
+        <v>144467.867503</v>
       </c>
       <c r="J130" t="n">
-        <v>158126.218308</v>
+        <v>158551.882511</v>
       </c>
       <c r="K130" t="n">
-        <v>170966.865554</v>
+        <v>171512.433829</v>
       </c>
       <c r="L130" t="n">
-        <v>180356.956675</v>
+        <v>181028.281879</v>
       </c>
       <c r="M130" t="n">
-        <v>185406.857447</v>
+        <v>186203.409179</v>
       </c>
       <c r="N130" t="n">
-        <v>186521.828356</v>
+        <v>187439.40123</v>
       </c>
       <c r="O130" t="n">
-        <v>184248.581279</v>
+        <v>185281.240177</v>
       </c>
       <c r="P130" t="n">
-        <v>179165.757492</v>
+        <v>180307.793223</v>
       </c>
       <c r="Q130" t="n">
-        <v>172174.061809</v>
+        <v>173422.107015</v>
       </c>
       <c r="R130" t="n">
-        <v>163830.493805</v>
+        <v>165180.639568</v>
       </c>
       <c r="S130" t="n">
-        <v>154414.7488</v>
+        <v>155859.693639</v>
       </c>
       <c r="T130" t="n">
-        <v>143955.501054</v>
+        <v>145482.375364</v>
       </c>
       <c r="U130" t="n">
-        <v>131935.68225</v>
+        <v>133519.285522</v>
       </c>
       <c r="V130" t="n">
-        <v>118794.577847</v>
+        <v>120404.1626</v>
       </c>
     </row>
     <row r="131">
@@ -10330,58 +10330,58 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>7196.308483</v>
+        <v>7197.79636</v>
       </c>
       <c r="F131" t="n">
-        <v>9400.92332</v>
+        <v>9405.733727000001</v>
       </c>
       <c r="G131" t="n">
-        <v>11621.73053</v>
+        <v>11631.390452</v>
       </c>
       <c r="H131" t="n">
-        <v>13391.3619</v>
+        <v>13406.76442</v>
       </c>
       <c r="I131" t="n">
-        <v>15005.410701</v>
+        <v>15027.312143</v>
       </c>
       <c r="J131" t="n">
-        <v>16543.377061</v>
+        <v>16572.556349</v>
       </c>
       <c r="K131" t="n">
-        <v>18006.076196</v>
+        <v>18043.195894</v>
       </c>
       <c r="L131" t="n">
-        <v>19108.738557</v>
+        <v>19153.918037</v>
       </c>
       <c r="M131" t="n">
-        <v>19679.876181</v>
+        <v>19732.384576</v>
       </c>
       <c r="N131" t="n">
-        <v>19720.8932</v>
+        <v>19779.365603</v>
       </c>
       <c r="O131" t="n">
-        <v>19407.418369</v>
+        <v>19470.858707</v>
       </c>
       <c r="P131" t="n">
-        <v>18895.390968</v>
+        <v>18963.49079</v>
       </c>
       <c r="Q131" t="n">
-        <v>18302.121643</v>
+        <v>18375.101473</v>
       </c>
       <c r="R131" t="n">
-        <v>17642.859106</v>
+        <v>17720.779561</v>
       </c>
       <c r="S131" t="n">
-        <v>16898.34047</v>
+        <v>16980.667599</v>
       </c>
       <c r="T131" t="n">
-        <v>16054.488947</v>
+        <v>16140.117506</v>
       </c>
       <c r="U131" t="n">
-        <v>15070.240532</v>
+        <v>15157.505253</v>
       </c>
       <c r="V131" t="n">
-        <v>14022.266426</v>
+        <v>14109.497578</v>
       </c>
     </row>
     <row r="132">
@@ -10406,58 +10406,58 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>155436.825189</v>
+        <v>155404.36081</v>
       </c>
       <c r="F132" t="n">
-        <v>165930.810193</v>
+        <v>165867.181915</v>
       </c>
       <c r="G132" t="n">
-        <v>180194.883413</v>
+        <v>180088.808085</v>
       </c>
       <c r="H132" t="n">
-        <v>187157.76943</v>
+        <v>187001.574803</v>
       </c>
       <c r="I132" t="n">
-        <v>192904.94507</v>
+        <v>192690.912247</v>
       </c>
       <c r="J132" t="n">
-        <v>199252.368695</v>
+        <v>198977.074133</v>
       </c>
       <c r="K132" t="n">
-        <v>208150.071124</v>
+        <v>207818.119656</v>
       </c>
       <c r="L132" t="n">
-        <v>215538.26904</v>
+        <v>215161.255491</v>
       </c>
       <c r="M132" t="n">
-        <v>218589.586299</v>
+        <v>218180.120573</v>
       </c>
       <c r="N132" t="n">
-        <v>217618.310402</v>
+        <v>217193.158252</v>
       </c>
       <c r="O132" t="n">
-        <v>214448.82038</v>
+        <v>214026.524981</v>
       </c>
       <c r="P132" t="n">
-        <v>209026.945206</v>
+        <v>208619.794539</v>
       </c>
       <c r="Q132" t="n">
-        <v>201181.619858</v>
+        <v>200788.669494</v>
       </c>
       <c r="R132" t="n">
-        <v>191571.628741</v>
+        <v>191186.320419</v>
       </c>
       <c r="S132" t="n">
-        <v>181588.662508</v>
+        <v>181206.352182</v>
       </c>
       <c r="T132" t="n">
-        <v>172475.307814</v>
+        <v>172097.268356</v>
       </c>
       <c r="U132" t="n">
-        <v>164336.258872</v>
+        <v>163970.23635</v>
       </c>
       <c r="V132" t="n">
-        <v>157674.179725</v>
+        <v>157328.166809</v>
       </c>
     </row>
     <row r="133">
@@ -10482,58 +10482,58 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>44928.483623</v>
+        <v>44901.892128</v>
       </c>
       <c r="F133" t="n">
-        <v>68230.079191</v>
+        <v>68184.10632799999</v>
       </c>
       <c r="G133" t="n">
-        <v>102347.449411</v>
+        <v>102292.937353</v>
       </c>
       <c r="H133" t="n">
-        <v>134931.002788</v>
+        <v>134876.321142</v>
       </c>
       <c r="I133" t="n">
-        <v>164013.682866</v>
+        <v>163953.988254</v>
       </c>
       <c r="J133" t="n">
-        <v>189695.142476</v>
+        <v>189615.290261</v>
       </c>
       <c r="K133" t="n">
-        <v>215143.191678</v>
+        <v>215026.611431</v>
       </c>
       <c r="L133" t="n">
-        <v>239596.545993</v>
+        <v>239431.226684</v>
       </c>
       <c r="M133" t="n">
-        <v>262605.126701</v>
+        <v>262388.003253</v>
       </c>
       <c r="N133" t="n">
-        <v>284310.758429</v>
+        <v>284046.398929</v>
       </c>
       <c r="O133" t="n">
-        <v>305983.413302</v>
+        <v>305680.398386</v>
       </c>
       <c r="P133" t="n">
-        <v>328406.691299</v>
+        <v>328077.920104</v>
       </c>
       <c r="Q133" t="n">
-        <v>352660.016484</v>
+        <v>352320.585808</v>
       </c>
       <c r="R133" t="n">
-        <v>378815.064815</v>
+        <v>378482.44922</v>
       </c>
       <c r="S133" t="n">
-        <v>406038.112719</v>
+        <v>405726.601294</v>
       </c>
       <c r="T133" t="n">
-        <v>433653.713808</v>
+        <v>433374.784149</v>
       </c>
       <c r="U133" t="n">
-        <v>460280.203498</v>
+        <v>460045.275323</v>
       </c>
       <c r="V133" t="n">
-        <v>488694.810369</v>
+        <v>488521.826052</v>
       </c>
     </row>
     <row r="134">
@@ -10558,58 +10558,58 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>8165.757503</v>
+        <v>8154.77947</v>
       </c>
       <c r="F134" t="n">
-        <v>8465.362714000001</v>
+        <v>8441.034937</v>
       </c>
       <c r="G134" t="n">
-        <v>9374.999599999999</v>
+        <v>9332.361188999999</v>
       </c>
       <c r="H134" t="n">
-        <v>10293.112269</v>
+        <v>10229.458655</v>
       </c>
       <c r="I134" t="n">
-        <v>11414.581919</v>
+        <v>11326.636619</v>
       </c>
       <c r="J134" t="n">
-        <v>12726.326762</v>
+        <v>12610.686667</v>
       </c>
       <c r="K134" t="n">
-        <v>14221.387165</v>
+        <v>14074.19899</v>
       </c>
       <c r="L134" t="n">
-        <v>15703.992003</v>
+        <v>15523.159978</v>
       </c>
       <c r="M134" t="n">
-        <v>17035.818251</v>
+        <v>16820.891481</v>
       </c>
       <c r="N134" t="n">
-        <v>18200.062427</v>
+        <v>17951.790639</v>
       </c>
       <c r="O134" t="n">
-        <v>19340.130216</v>
+        <v>19058.184897</v>
       </c>
       <c r="P134" t="n">
-        <v>20573.879394</v>
+        <v>20257.442139</v>
       </c>
       <c r="Q134" t="n">
-        <v>22008.987122</v>
+        <v>21656.181847</v>
       </c>
       <c r="R134" t="n">
-        <v>23665.689707</v>
+        <v>23274.660166</v>
       </c>
       <c r="S134" t="n">
-        <v>25557.699622</v>
+        <v>25127.331969</v>
       </c>
       <c r="T134" t="n">
-        <v>27710.399021</v>
+        <v>27240.84723</v>
       </c>
       <c r="U134" t="n">
-        <v>30125.393783</v>
+        <v>29620.072674</v>
       </c>
       <c r="V134" t="n">
-        <v>33062.212966</v>
+        <v>32527.04225</v>
       </c>
     </row>
     <row r="135">
@@ -10634,58 +10634,58 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>3493.937996</v>
+        <v>3485.485553</v>
       </c>
       <c r="F135" t="n">
-        <v>4911.418542</v>
+        <v>4892.474558</v>
       </c>
       <c r="G135" t="n">
-        <v>7015.631346</v>
+        <v>6981.937734</v>
       </c>
       <c r="H135" t="n">
-        <v>9098.512853</v>
+        <v>9047.016776</v>
       </c>
       <c r="I135" t="n">
-        <v>11192.175769</v>
+        <v>11119.242862</v>
       </c>
       <c r="J135" t="n">
-        <v>13371.571536</v>
+        <v>13273.143884</v>
       </c>
       <c r="K135" t="n">
-        <v>15777.282086</v>
+        <v>15648.304603</v>
       </c>
       <c r="L135" t="n">
-        <v>18301.087001</v>
+        <v>18137.29504</v>
       </c>
       <c r="M135" t="n">
-        <v>20829.319969</v>
+        <v>20628.189488</v>
       </c>
       <c r="N135" t="n">
-        <v>23255.705363</v>
+        <v>23016.212411</v>
       </c>
       <c r="O135" t="n">
-        <v>25605.989657</v>
+        <v>25327.78344</v>
       </c>
       <c r="P135" t="n">
-        <v>27932.378431</v>
+        <v>27614.735704</v>
       </c>
       <c r="Q135" t="n">
-        <v>30384.009901</v>
+        <v>30024.82509</v>
       </c>
       <c r="R135" t="n">
-        <v>33028.556304</v>
+        <v>32625.293953</v>
       </c>
       <c r="S135" t="n">
-        <v>35873.945753</v>
+        <v>35424.815757</v>
       </c>
       <c r="T135" t="n">
-        <v>38904.399915</v>
+        <v>38409.333143</v>
       </c>
       <c r="U135" t="n">
-        <v>42058.227365</v>
+        <v>41521.234608</v>
       </c>
       <c r="V135" t="n">
-        <v>45675.676654</v>
+        <v>45103.035645</v>
       </c>
     </row>
     <row r="136">
@@ -10710,58 +10710,58 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>25914.447484</v>
+        <v>25924.707738</v>
       </c>
       <c r="F136" t="n">
-        <v>25952.109348</v>
+        <v>25971.490799</v>
       </c>
       <c r="G136" t="n">
-        <v>25753.827795</v>
+        <v>25780.086686</v>
       </c>
       <c r="H136" t="n">
-        <v>24581.593529</v>
+        <v>24610.697799</v>
       </c>
       <c r="I136" t="n">
-        <v>24100.292484</v>
+        <v>24131.14905</v>
       </c>
       <c r="J136" t="n">
-        <v>25249.158454</v>
+        <v>25285.651898</v>
       </c>
       <c r="K136" t="n">
-        <v>27170.398914</v>
+        <v>27215.924168</v>
       </c>
       <c r="L136" t="n">
-        <v>29126.879218</v>
+        <v>29184.397754</v>
       </c>
       <c r="M136" t="n">
-        <v>30878.010974</v>
+        <v>30950.771528</v>
       </c>
       <c r="N136" t="n">
-        <v>31901.332219</v>
+        <v>31989.687947</v>
       </c>
       <c r="O136" t="n">
-        <v>32235.217746</v>
+        <v>32338.801468</v>
       </c>
       <c r="P136" t="n">
-        <v>32071.564799</v>
+        <v>32190.560617</v>
       </c>
       <c r="Q136" t="n">
-        <v>31602.577658</v>
+        <v>31737.801381</v>
       </c>
       <c r="R136" t="n">
-        <v>30913.937976</v>
+        <v>31066.309512</v>
       </c>
       <c r="S136" t="n">
-        <v>30001.419555</v>
+        <v>30171.114039</v>
       </c>
       <c r="T136" t="n">
-        <v>28805.953403</v>
+        <v>28991.668992</v>
       </c>
       <c r="U136" t="n">
-        <v>27208.107547</v>
+        <v>27406.448069</v>
       </c>
       <c r="V136" t="n">
-        <v>25334.443305</v>
+        <v>25541.207423</v>
       </c>
     </row>
     <row r="137">
@@ -10786,58 +10786,58 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>2787.723154</v>
+        <v>2781.600422</v>
       </c>
       <c r="F137" t="n">
-        <v>3182.50598</v>
+        <v>3170.08197</v>
       </c>
       <c r="G137" t="n">
-        <v>3566.423459</v>
+        <v>3546.150794</v>
       </c>
       <c r="H137" t="n">
-        <v>3811.844256</v>
+        <v>3783.387477</v>
       </c>
       <c r="I137" t="n">
-        <v>4089.867969</v>
+        <v>4052.843534</v>
       </c>
       <c r="J137" t="n">
-        <v>4415.019872</v>
+        <v>4369.185251</v>
       </c>
       <c r="K137" t="n">
-        <v>4775.149875</v>
+        <v>4720.202828</v>
       </c>
       <c r="L137" t="n">
-        <v>5081.68767</v>
+        <v>5018.007545</v>
       </c>
       <c r="M137" t="n">
-        <v>5281.934858</v>
+        <v>5210.516952</v>
       </c>
       <c r="N137" t="n">
-        <v>5365.677385</v>
+        <v>5287.867976</v>
       </c>
       <c r="O137" t="n">
-        <v>5373.030245</v>
+        <v>5290.054662</v>
       </c>
       <c r="P137" t="n">
-        <v>5345.809292</v>
+        <v>5258.681775</v>
       </c>
       <c r="Q137" t="n">
-        <v>5322.849202</v>
+        <v>5232.190098</v>
       </c>
       <c r="R137" t="n">
-        <v>5314.672137</v>
+        <v>5220.997454</v>
       </c>
       <c r="S137" t="n">
-        <v>5319.616527</v>
+        <v>5223.534543</v>
       </c>
       <c r="T137" t="n">
-        <v>5339.005909</v>
+        <v>5241.292634</v>
       </c>
       <c r="U137" t="n">
-        <v>5375.188204</v>
+        <v>5277.171854</v>
       </c>
       <c r="V137" t="n">
-        <v>5482.938671</v>
+        <v>5386.015346</v>
       </c>
     </row>
     <row r="138">
@@ -10862,58 +10862,58 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>27576.593717</v>
+        <v>27589.037542</v>
       </c>
       <c r="F138" t="n">
-        <v>29346.786155</v>
+        <v>29373.359538</v>
       </c>
       <c r="G138" t="n">
-        <v>31665.14419</v>
+        <v>31708.344689</v>
       </c>
       <c r="H138" t="n">
-        <v>32230.315516</v>
+        <v>32288.287454</v>
       </c>
       <c r="I138" t="n">
-        <v>32169.608373</v>
+        <v>32240.350859</v>
       </c>
       <c r="J138" t="n">
-        <v>32073.877255</v>
+        <v>32156.580808</v>
       </c>
       <c r="K138" t="n">
-        <v>32277.584486</v>
+        <v>32373.084003</v>
       </c>
       <c r="L138" t="n">
-        <v>32378.918329</v>
+        <v>32488.030322</v>
       </c>
       <c r="M138" t="n">
-        <v>32088.030349</v>
+        <v>32210.590912</v>
       </c>
       <c r="N138" t="n">
-        <v>31436.29934</v>
+        <v>31571.988413</v>
       </c>
       <c r="O138" t="n">
-        <v>30526.345335</v>
+        <v>30674.923348</v>
       </c>
       <c r="P138" t="n">
-        <v>29366.983924</v>
+        <v>29527.962633</v>
       </c>
       <c r="Q138" t="n">
-        <v>28050.126555</v>
+        <v>28223.137139</v>
       </c>
       <c r="R138" t="n">
-        <v>26700.941803</v>
+        <v>26886.302008</v>
       </c>
       <c r="S138" t="n">
-        <v>25285.50343</v>
+        <v>25482.544973</v>
       </c>
       <c r="T138" t="n">
-        <v>23770.37488</v>
+        <v>23977.356827</v>
       </c>
       <c r="U138" t="n">
-        <v>22092.769342</v>
+        <v>22306.700737</v>
       </c>
       <c r="V138" t="n">
-        <v>20353.278208</v>
+        <v>20571.053783</v>
       </c>
     </row>
     <row r="139">
@@ -10938,58 +10938,58 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>62571.605492</v>
+        <v>62609.247329</v>
       </c>
       <c r="F139" t="n">
-        <v>70173.77271200001</v>
+        <v>70258.932698</v>
       </c>
       <c r="G139" t="n">
-        <v>82736.780222</v>
+        <v>82891.21049500001</v>
       </c>
       <c r="H139" t="n">
-        <v>93840.84491499999</v>
+        <v>94079.325018</v>
       </c>
       <c r="I139" t="n">
-        <v>104284.289972</v>
+        <v>104621.277726</v>
       </c>
       <c r="J139" t="n">
-        <v>113384.806091</v>
+        <v>113831.525342</v>
       </c>
       <c r="K139" t="n">
-        <v>121372.741404</v>
+        <v>121940.071564</v>
       </c>
       <c r="L139" t="n">
-        <v>126631.601292</v>
+        <v>127323.357252</v>
       </c>
       <c r="M139" t="n">
-        <v>128661.147423</v>
+        <v>129474.220901</v>
       </c>
       <c r="N139" t="n">
-        <v>127870.978033</v>
+        <v>128798.263802</v>
       </c>
       <c r="O139" t="n">
-        <v>124907.864961</v>
+        <v>125941.722114</v>
       </c>
       <c r="P139" t="n">
-        <v>120065.21487</v>
+        <v>121197.640085</v>
       </c>
       <c r="Q139" t="n">
-        <v>113907.1502</v>
+        <v>115132.540698</v>
       </c>
       <c r="R139" t="n">
-        <v>106806.457171</v>
+        <v>108119.128696</v>
       </c>
       <c r="S139" t="n">
-        <v>99017.365314</v>
+        <v>100409.838248</v>
       </c>
       <c r="T139" t="n">
-        <v>90601.707251</v>
+        <v>92062.790996</v>
       </c>
       <c r="U139" t="n">
-        <v>81209.740727</v>
+        <v>82717.75663600001</v>
       </c>
       <c r="V139" t="n">
-        <v>70998.110837</v>
+        <v>72526.434693</v>
       </c>
     </row>
     <row r="140">
@@ -11014,58 +11014,58 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>175354.08323</v>
+        <v>175410.442681</v>
       </c>
       <c r="F140" t="n">
-        <v>180517.930268</v>
+        <v>180625.228977</v>
       </c>
       <c r="G140" t="n">
-        <v>198702.92929</v>
+        <v>198870.73637</v>
       </c>
       <c r="H140" t="n">
-        <v>218711.085599</v>
+        <v>218950.167085</v>
       </c>
       <c r="I140" t="n">
-        <v>245579.810562</v>
+        <v>245916.486273</v>
       </c>
       <c r="J140" t="n">
-        <v>279381.211493</v>
+        <v>279854.441381</v>
       </c>
       <c r="K140" t="n">
-        <v>318799.468144</v>
+        <v>319453.676794</v>
       </c>
       <c r="L140" t="n">
-        <v>357492.708659</v>
+        <v>358365.860842</v>
       </c>
       <c r="M140" t="n">
-        <v>390735.443557</v>
+        <v>391852.056382</v>
       </c>
       <c r="N140" t="n">
-        <v>416261.156001</v>
+        <v>417629.406242</v>
       </c>
       <c r="O140" t="n">
-        <v>435444.455337</v>
+        <v>437072.284949</v>
       </c>
       <c r="P140" t="n">
-        <v>450616.939346</v>
+        <v>452524.768725</v>
       </c>
       <c r="Q140" t="n">
-        <v>464863.030626</v>
+        <v>467094.582811</v>
       </c>
       <c r="R140" t="n">
-        <v>478583.363602</v>
+        <v>481191.582693</v>
       </c>
       <c r="S140" t="n">
-        <v>491175.9989</v>
+        <v>494216.147706</v>
       </c>
       <c r="T140" t="n">
-        <v>500991.753103</v>
+        <v>504507.602943</v>
       </c>
       <c r="U140" t="n">
-        <v>505085.484725</v>
+        <v>509092.563531</v>
       </c>
       <c r="V140" t="n">
-        <v>504119.05036</v>
+        <v>508613.809643</v>
       </c>
     </row>
     <row r="141">
@@ -11090,58 +11090,58 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>4531.660529</v>
+        <v>4502.039377</v>
       </c>
       <c r="F141" t="n">
-        <v>5839.602897</v>
+        <v>5774.616966</v>
       </c>
       <c r="G141" t="n">
-        <v>7770.749416</v>
+        <v>7656.208922</v>
       </c>
       <c r="H141" t="n">
-        <v>9797.721079000001</v>
+        <v>9624.186261999999</v>
       </c>
       <c r="I141" t="n">
-        <v>12029.659598</v>
+        <v>11787.036</v>
       </c>
       <c r="J141" t="n">
-        <v>14490.079137</v>
+        <v>14167.957368</v>
       </c>
       <c r="K141" t="n">
-        <v>17265.688745</v>
+        <v>16851.05115</v>
       </c>
       <c r="L141" t="n">
-        <v>20251.851017</v>
+        <v>19733.740313</v>
       </c>
       <c r="M141" t="n">
-        <v>23356.186309</v>
+        <v>22727.843855</v>
       </c>
       <c r="N141" t="n">
-        <v>26561.036617</v>
+        <v>25819.531334</v>
       </c>
       <c r="O141" t="n">
-        <v>30013.413944</v>
+        <v>29154.646199</v>
       </c>
       <c r="P141" t="n">
-        <v>33878.041168</v>
+        <v>32895.188818</v>
       </c>
       <c r="Q141" t="n">
-        <v>38422.570157</v>
+        <v>37303.048764</v>
       </c>
       <c r="R141" t="n">
-        <v>43827.660542</v>
+        <v>42556.558301</v>
       </c>
       <c r="S141" t="n">
-        <v>50183.058862</v>
+        <v>48747.193314</v>
       </c>
       <c r="T141" t="n">
-        <v>57644.987046</v>
+        <v>56035.865807</v>
       </c>
       <c r="U141" t="n">
-        <v>66409.415118</v>
+        <v>64630.191382</v>
       </c>
       <c r="V141" t="n">
-        <v>77476.786345</v>
+        <v>75536.281246</v>
       </c>
     </row>
     <row r="142">
@@ -11166,58 +11166,58 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>4063.546619</v>
+        <v>4027.445389</v>
       </c>
       <c r="F142" t="n">
-        <v>7884.513364</v>
+        <v>7796.289391</v>
       </c>
       <c r="G142" t="n">
-        <v>15440.764252</v>
+        <v>15270.574269</v>
       </c>
       <c r="H142" t="n">
-        <v>25027.682886</v>
+        <v>24753.966357</v>
       </c>
       <c r="I142" t="n">
-        <v>35225.469127</v>
+        <v>34824.845927</v>
       </c>
       <c r="J142" t="n">
-        <v>45178.672883</v>
+        <v>44621.854169</v>
       </c>
       <c r="K142" t="n">
-        <v>55223.67075</v>
+        <v>54472.701213</v>
       </c>
       <c r="L142" t="n">
-        <v>65365.756817</v>
+        <v>64386.461136</v>
       </c>
       <c r="M142" t="n">
-        <v>75578.943912</v>
+        <v>74347.283152</v>
       </c>
       <c r="N142" t="n">
-        <v>85967.79905</v>
+        <v>84468.764044</v>
       </c>
       <c r="O142" t="n">
-        <v>96916.02815</v>
+        <v>95133.285594</v>
       </c>
       <c r="P142" t="n">
-        <v>108808.331375</v>
+        <v>106717.948413</v>
       </c>
       <c r="Q142" t="n">
-        <v>122207.653895</v>
+        <v>119776.00349</v>
       </c>
       <c r="R142" t="n">
-        <v>137508.953551</v>
+        <v>134699.257708</v>
       </c>
       <c r="S142" t="n">
-        <v>155023.263855</v>
+        <v>151801.901051</v>
       </c>
       <c r="T142" t="n">
-        <v>175065.118744</v>
+        <v>171411.406946</v>
       </c>
       <c r="U142" t="n">
-        <v>197886.796452</v>
+        <v>193809.066477</v>
       </c>
       <c r="V142" t="n">
-        <v>226056.33982</v>
+        <v>221576.138464</v>
       </c>
     </row>
     <row r="143">
@@ -11470,58 +11470,58 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>156.47497</v>
+        <v>155.650681</v>
       </c>
       <c r="F146" t="n">
-        <v>157.083424</v>
+        <v>155.616915</v>
       </c>
       <c r="G146" t="n">
-        <v>159.318121</v>
+        <v>157.279155</v>
       </c>
       <c r="H146" t="n">
-        <v>162.586211</v>
+        <v>160.089522</v>
       </c>
       <c r="I146" t="n">
-        <v>167.512451</v>
+        <v>164.652073</v>
       </c>
       <c r="J146" t="n">
-        <v>172.242461</v>
+        <v>169.108762</v>
       </c>
       <c r="K146" t="n">
-        <v>180.085838</v>
+        <v>176.665295</v>
       </c>
       <c r="L146" t="n">
-        <v>190.099962</v>
+        <v>186.382827</v>
       </c>
       <c r="M146" t="n">
-        <v>199.743234</v>
+        <v>195.760796</v>
       </c>
       <c r="N146" t="n">
-        <v>206.947072</v>
+        <v>202.768466</v>
       </c>
       <c r="O146" t="n">
-        <v>211.889576</v>
+        <v>207.573006</v>
       </c>
       <c r="P146" t="n">
-        <v>215.776005</v>
+        <v>211.361317</v>
       </c>
       <c r="Q146" t="n">
-        <v>218.798728</v>
+        <v>214.32505</v>
       </c>
       <c r="R146" t="n">
-        <v>221.312854</v>
+        <v>216.807894</v>
       </c>
       <c r="S146" t="n">
-        <v>223.489845</v>
+        <v>218.971621</v>
       </c>
       <c r="T146" t="n">
-        <v>224.988485</v>
+        <v>220.474798</v>
       </c>
       <c r="U146" t="n">
-        <v>225.659534</v>
+        <v>221.163031</v>
       </c>
       <c r="V146" t="n">
-        <v>226.521932</v>
+        <v>222.032382</v>
       </c>
     </row>
     <row r="147">
@@ -11546,58 +11546,58 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>87.992475</v>
+        <v>87.36160599999999</v>
       </c>
       <c r="F147" t="n">
-        <v>102.376042</v>
+        <v>101.236584</v>
       </c>
       <c r="G147" t="n">
-        <v>115.829195</v>
+        <v>114.211686</v>
       </c>
       <c r="H147" t="n">
-        <v>124.72407</v>
+        <v>122.682998</v>
       </c>
       <c r="I147" t="n">
-        <v>131.587654</v>
+        <v>129.164664</v>
       </c>
       <c r="J147" t="n">
-        <v>136.959169</v>
+        <v>134.198787</v>
       </c>
       <c r="K147" t="n">
-        <v>145.300878</v>
+        <v>142.165139</v>
       </c>
       <c r="L147" t="n">
-        <v>155.395008</v>
+        <v>151.847508</v>
       </c>
       <c r="M147" t="n">
-        <v>165.329038</v>
+        <v>161.370996</v>
       </c>
       <c r="N147" t="n">
-        <v>173.596046</v>
+        <v>169.268162</v>
       </c>
       <c r="O147" t="n">
-        <v>179.718006</v>
+        <v>175.074545</v>
       </c>
       <c r="P147" t="n">
-        <v>184.40399</v>
+        <v>179.486613</v>
       </c>
       <c r="Q147" t="n">
-        <v>187.912879</v>
+        <v>182.765013</v>
       </c>
       <c r="R147" t="n">
-        <v>190.772134</v>
+        <v>185.426552</v>
       </c>
       <c r="S147" t="n">
-        <v>193.2933</v>
+        <v>187.772649</v>
       </c>
       <c r="T147" t="n">
-        <v>195.229181</v>
+        <v>189.560848</v>
       </c>
       <c r="U147" t="n">
-        <v>196.379643</v>
+        <v>190.598236</v>
       </c>
       <c r="V147" t="n">
-        <v>197.33824</v>
+        <v>191.462509</v>
       </c>
     </row>
     <row r="148">
@@ -11622,58 +11622,58 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>52123.078758</v>
+        <v>52124.533916</v>
       </c>
       <c r="F148" t="n">
-        <v>57095.38869</v>
+        <v>57097.994658</v>
       </c>
       <c r="G148" t="n">
-        <v>63780.506078</v>
+        <v>63784.162554</v>
       </c>
       <c r="H148" t="n">
-        <v>67605.853481</v>
+        <v>67610.39124300001</v>
       </c>
       <c r="I148" t="n">
-        <v>68955.099334</v>
+        <v>68960.382702</v>
       </c>
       <c r="J148" t="n">
-        <v>68504.199836</v>
+        <v>68510.09391700001</v>
       </c>
       <c r="K148" t="n">
-        <v>68800.578974</v>
+        <v>68807.13525599999</v>
       </c>
       <c r="L148" t="n">
-        <v>69487.90583</v>
+        <v>69495.170465</v>
       </c>
       <c r="M148" t="n">
-        <v>69842.249045</v>
+        <v>69850.189524</v>
       </c>
       <c r="N148" t="n">
-        <v>69570.11246600001</v>
+        <v>69578.618957</v>
       </c>
       <c r="O148" t="n">
-        <v>68683.13153</v>
+        <v>68692.09156099999</v>
       </c>
       <c r="P148" t="n">
-        <v>67402.146865</v>
+        <v>67411.47893100001</v>
       </c>
       <c r="Q148" t="n">
-        <v>65680.30310600001</v>
+        <v>65689.924648</v>
       </c>
       <c r="R148" t="n">
-        <v>63746.482563</v>
+        <v>63756.333105</v>
       </c>
       <c r="S148" t="n">
-        <v>61712.109274</v>
+        <v>61722.148148</v>
       </c>
       <c r="T148" t="n">
-        <v>59580.933873</v>
+        <v>59591.115892</v>
       </c>
       <c r="U148" t="n">
-        <v>57324.84938</v>
+        <v>57335.12729</v>
       </c>
       <c r="V148" t="n">
-        <v>55092.211058</v>
+        <v>55102.57634</v>
       </c>
     </row>
     <row r="149">
@@ -11698,19 +11698,19 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>5012.402076</v>
+        <v>5011.901761</v>
       </c>
       <c r="F149" t="n">
-        <v>5672.001976</v>
+        <v>5670.013309</v>
       </c>
       <c r="G149" t="n">
-        <v>6780.982401</v>
+        <v>6775.666852</v>
       </c>
       <c r="H149" t="n">
-        <v>7961.121945</v>
+        <v>7950.410791</v>
       </c>
       <c r="I149" t="n">
-        <v>9405.135259000001</v>
+        <v>9385.492874</v>
       </c>
       <c r="J149" t="n">
         <v>11869.08621</v>
@@ -11774,19 +11774,19 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>21460.862455</v>
+        <v>21470.57518</v>
       </c>
       <c r="F150" t="n">
-        <v>23788.953644</v>
+        <v>23812.925332</v>
       </c>
       <c r="G150" t="n">
-        <v>27461.829797</v>
+        <v>27512.33084</v>
       </c>
       <c r="H150" t="n">
-        <v>29694.056744</v>
+        <v>29791.332292</v>
       </c>
       <c r="I150" t="n">
-        <v>30957.63725</v>
+        <v>31153.230039</v>
       </c>
       <c r="J150" t="n">
         <v>25490.722374</v>
@@ -11850,19 +11850,19 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>10291.627472</v>
+        <v>10292.427813</v>
       </c>
       <c r="F151" t="n">
-        <v>11923.852088</v>
+        <v>11925.809165</v>
       </c>
       <c r="G151" t="n">
-        <v>14440.520695</v>
+        <v>14445.514275</v>
       </c>
       <c r="H151" t="n">
-        <v>16417.257652</v>
+        <v>16429.155796</v>
       </c>
       <c r="I151" t="n">
-        <v>17947.166684</v>
+        <v>17973.116326</v>
       </c>
       <c r="J151" t="n">
         <v>18687.634066</v>
@@ -11926,19 +11926,19 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>18341.496715</v>
+        <v>18336.872651</v>
       </c>
       <c r="F152" t="n">
-        <v>22326.04571</v>
+        <v>22316.278276</v>
       </c>
       <c r="G152" t="n">
-        <v>26680.133073</v>
+        <v>26660.99851</v>
       </c>
       <c r="H152" t="n">
-        <v>29328.596877</v>
+        <v>29292.047181</v>
       </c>
       <c r="I152" t="n">
-        <v>31362.566255</v>
+        <v>31287.092821</v>
       </c>
       <c r="J152" t="n">
         <v>36709.463493</v>
@@ -12002,19 +12002,19 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>943.758701</v>
+        <v>940.10814</v>
       </c>
       <c r="F153" t="n">
-        <v>1128.508043</v>
+        <v>1118.612165</v>
       </c>
       <c r="G153" t="n">
-        <v>1491.948517</v>
+        <v>1469.628804</v>
       </c>
       <c r="H153" t="n">
-        <v>2000.639499</v>
+        <v>1954.898453</v>
       </c>
       <c r="I153" t="n">
-        <v>2946.906117</v>
+        <v>2851.415129</v>
       </c>
       <c r="J153" t="n">
         <v>7752.528</v>
@@ -12078,19 +12078,19 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>1684.832794</v>
+        <v>1683.094669</v>
       </c>
       <c r="F154" t="n">
-        <v>2034.399086</v>
+        <v>2030.122301</v>
       </c>
       <c r="G154" t="n">
-        <v>2463.195452</v>
+        <v>2454.470655</v>
       </c>
       <c r="H154" t="n">
-        <v>2776.724119</v>
+        <v>2760.552322</v>
       </c>
       <c r="I154" t="n">
-        <v>3109.982891</v>
+        <v>3079.047268</v>
       </c>
       <c r="J154" t="n">
         <v>4550.02258</v>
@@ -12154,19 +12154,19 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>2842.863803</v>
+        <v>2842.86676</v>
       </c>
       <c r="F155" t="n">
-        <v>4454.577991</v>
+        <v>4454.575334</v>
       </c>
       <c r="G155" t="n">
-        <v>6441.774039</v>
+        <v>6441.72683</v>
       </c>
       <c r="H155" t="n">
-        <v>8618.402748</v>
+        <v>8618.208124000001</v>
       </c>
       <c r="I155" t="n">
-        <v>10734.566735</v>
+        <v>10733.851971</v>
       </c>
       <c r="J155" t="n">
         <v>13898.594972</v>
@@ -12230,19 +12230,19 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>26420.001417</v>
+        <v>26420.274958</v>
       </c>
       <c r="F156" t="n">
-        <v>38595.37414</v>
+        <v>38596.248853</v>
       </c>
       <c r="G156" t="n">
-        <v>51252.468396</v>
+        <v>51254.472378</v>
       </c>
       <c r="H156" t="n">
-        <v>61938.156948</v>
+        <v>61942.481793</v>
       </c>
       <c r="I156" t="n">
-        <v>69387.58261</v>
+        <v>69398.751518</v>
       </c>
       <c r="J156" t="n">
         <v>68100.48211899999</v>
@@ -12306,19 +12306,19 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>847.231734</v>
+        <v>847.257059</v>
       </c>
       <c r="F157" t="n">
-        <v>1560.297864</v>
+        <v>1560.409472</v>
       </c>
       <c r="G157" t="n">
-        <v>2524.754992</v>
+        <v>2525.100363</v>
       </c>
       <c r="H157" t="n">
-        <v>3416.829926</v>
+        <v>3417.734069</v>
       </c>
       <c r="I157" t="n">
-        <v>3995.650781</v>
+        <v>3998.218412</v>
       </c>
       <c r="J157" t="n">
         <v>2370.071589</v>
@@ -12382,19 +12382,19 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>2338.857</v>
+        <v>2338.512417</v>
       </c>
       <c r="F158" t="n">
-        <v>3033.394262</v>
+        <v>3032.271449</v>
       </c>
       <c r="G158" t="n">
-        <v>3555.171211</v>
+        <v>3552.532785</v>
       </c>
       <c r="H158" t="n">
-        <v>3945.023344</v>
+        <v>3939.207979</v>
       </c>
       <c r="I158" t="n">
-        <v>4269.202828</v>
+        <v>4253.996845</v>
       </c>
       <c r="J158" t="n">
         <v>16487.087535</v>
@@ -12458,19 +12458,19 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>196.578968</v>
+        <v>196.581709</v>
       </c>
       <c r="F159" t="n">
-        <v>276.225042</v>
+        <v>276.233765</v>
       </c>
       <c r="G159" t="n">
-        <v>359.108509</v>
+        <v>359.128916</v>
       </c>
       <c r="H159" t="n">
-        <v>426.966094</v>
+        <v>427.010934</v>
       </c>
       <c r="I159" t="n">
-        <v>475.232472</v>
+        <v>475.350149</v>
       </c>
       <c r="J159" t="n">
         <v>431.731368</v>
@@ -12534,19 +12534,19 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>4385.85477</v>
+        <v>4385.894788</v>
       </c>
       <c r="F160" t="n">
-        <v>6661.467519</v>
+        <v>6661.597945</v>
       </c>
       <c r="G160" t="n">
-        <v>9577.962246999999</v>
+        <v>9578.278120999999</v>
       </c>
       <c r="H160" t="n">
-        <v>12745.462566</v>
+        <v>12746.198727</v>
       </c>
       <c r="I160" t="n">
-        <v>15714.729404</v>
+        <v>15716.795935</v>
       </c>
       <c r="J160" t="n">
         <v>17128.728617</v>
@@ -12686,19 +12686,19 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>4016.568527</v>
+        <v>4018.55263</v>
       </c>
       <c r="F162" t="n">
-        <v>3137.042215</v>
+        <v>3140.326831</v>
       </c>
       <c r="G162" t="n">
-        <v>2487.236853</v>
+        <v>2491.533724</v>
       </c>
       <c r="H162" t="n">
-        <v>2135.416113</v>
+        <v>2141.489125</v>
       </c>
       <c r="I162" t="n">
-        <v>1935.042752</v>
+        <v>1945.749102</v>
       </c>
       <c r="J162" t="n">
         <v>1134.019064</v>
@@ -12762,19 +12762,19 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>303.764607</v>
+        <v>303.392037</v>
       </c>
       <c r="F163" t="n">
-        <v>396.322927</v>
+        <v>395.319838</v>
       </c>
       <c r="G163" t="n">
-        <v>520.9534619999999</v>
+        <v>518.839213</v>
       </c>
       <c r="H163" t="n">
-        <v>641.554698</v>
+        <v>637.376653</v>
       </c>
       <c r="I163" t="n">
-        <v>782.1382149999999</v>
+        <v>773.272522</v>
       </c>
       <c r="J163" t="n">
         <v>1580.233675</v>
@@ -12838,19 +12838,19 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>1343.37584</v>
+        <v>1337.556664</v>
       </c>
       <c r="F164" t="n">
-        <v>2000.143694</v>
+        <v>1983.221164</v>
       </c>
       <c r="G164" t="n">
-        <v>2946.228734</v>
+        <v>2907.980218</v>
       </c>
       <c r="H164" t="n">
-        <v>4212.5286</v>
+        <v>4132.092565</v>
       </c>
       <c r="I164" t="n">
-        <v>6461.48648</v>
+        <v>6281.300789</v>
       </c>
       <c r="J164" t="n">
         <v>23159.136272</v>
@@ -12914,19 +12914,19 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>3288.087506</v>
+        <v>3286.694165</v>
       </c>
       <c r="F165" t="n">
-        <v>4125.406</v>
+        <v>4121.585599</v>
       </c>
       <c r="G165" t="n">
-        <v>4599.152458</v>
+        <v>4590.674928</v>
       </c>
       <c r="H165" t="n">
-        <v>5074.822197</v>
+        <v>5057.027812</v>
       </c>
       <c r="I165" t="n">
-        <v>5797.305693</v>
+        <v>5757.286863</v>
       </c>
       <c r="J165" t="n">
         <v>9902.220912000001</v>
@@ -12990,19 +12990,19 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>8034.107755</v>
+        <v>8022.125115</v>
       </c>
       <c r="F166" t="n">
-        <v>9570.54019</v>
+        <v>9539.031485</v>
       </c>
       <c r="G166" t="n">
-        <v>11213.185035</v>
+        <v>11148.609981</v>
       </c>
       <c r="H166" t="n">
-        <v>13077.03724</v>
+        <v>12951.176655</v>
       </c>
       <c r="I166" t="n">
-        <v>16116.243383</v>
+        <v>15851.098841</v>
       </c>
       <c r="J166" t="n">
         <v>39298.344163</v>
@@ -13066,19 +13066,19 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>92375.879052</v>
+        <v>92408.11378099999</v>
       </c>
       <c r="F167" t="n">
-        <v>102205.433684</v>
+        <v>102285.509751</v>
       </c>
       <c r="G167" t="n">
-        <v>112262.405515</v>
+        <v>112419.841458</v>
       </c>
       <c r="H167" t="n">
-        <v>122892.948765</v>
+        <v>123202.400587</v>
       </c>
       <c r="I167" t="n">
-        <v>130727.066639</v>
+        <v>131415.532365</v>
       </c>
       <c r="J167" t="n">
         <v>83679.353684</v>
@@ -13142,19 +13142,19 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>1690.608854</v>
+        <v>1691.587414</v>
       </c>
       <c r="F168" t="n">
-        <v>2039.320058</v>
+        <v>2042.075388</v>
       </c>
       <c r="G168" t="n">
-        <v>2380.003138</v>
+        <v>2385.982671</v>
       </c>
       <c r="H168" t="n">
-        <v>2650.31936</v>
+        <v>2662.61238</v>
       </c>
       <c r="I168" t="n">
-        <v>2728.90089</v>
+        <v>2756.369092</v>
       </c>
       <c r="J168" t="n">
         <v>582.803437</v>
@@ -13218,19 +13218,19 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>29441.246008</v>
+        <v>29408.460048</v>
       </c>
       <c r="F169" t="n">
-        <v>35868.173527</v>
+        <v>35776.285621</v>
       </c>
       <c r="G169" t="n">
-        <v>43125.818698</v>
+        <v>42923.841516</v>
       </c>
       <c r="H169" t="n">
-        <v>53368.120705</v>
+        <v>52940.967981</v>
       </c>
       <c r="I169" t="n">
-        <v>71059.62248400001</v>
+        <v>70074.484748</v>
       </c>
       <c r="J169" t="n">
         <v>175113.303479</v>
@@ -13294,19 +13294,19 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>1481.190867</v>
+        <v>1477.936497</v>
       </c>
       <c r="F170" t="n">
-        <v>2291.152142</v>
+        <v>2281.209236</v>
       </c>
       <c r="G170" t="n">
-        <v>3313.060552</v>
+        <v>3289.814141</v>
       </c>
       <c r="H170" t="n">
-        <v>4505.654508</v>
+        <v>4455.041126</v>
       </c>
       <c r="I170" t="n">
-        <v>6318.673637</v>
+        <v>6201.153906</v>
       </c>
       <c r="J170" t="n">
         <v>18060.452808</v>
@@ -13370,19 +13370,19 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>18524.718602</v>
+        <v>18518.991712</v>
       </c>
       <c r="F171" t="n">
-        <v>21571.070761</v>
+        <v>21556.376292</v>
       </c>
       <c r="G171" t="n">
-        <v>24557.598581</v>
+        <v>24527.745898</v>
       </c>
       <c r="H171" t="n">
-        <v>27224.785611</v>
+        <v>27166.927733</v>
       </c>
       <c r="I171" t="n">
-        <v>29977.172219</v>
+        <v>29855.964051</v>
       </c>
       <c r="J171" t="n">
         <v>41834.118508</v>
@@ -13446,19 +13446,19 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>31135.873923</v>
+        <v>31144.977408</v>
       </c>
       <c r="F172" t="n">
-        <v>34491.797218</v>
+        <v>34514.637971</v>
       </c>
       <c r="G172" t="n">
-        <v>36226.366609</v>
+        <v>36268.191419</v>
       </c>
       <c r="H172" t="n">
-        <v>37171.191836</v>
+        <v>37244.803166</v>
       </c>
       <c r="I172" t="n">
-        <v>37523.075497</v>
+        <v>37671.217012</v>
       </c>
       <c r="J172" t="n">
         <v>27404.027374</v>
@@ -13522,19 +13522,19 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>48.217673</v>
+        <v>47.968717</v>
       </c>
       <c r="F173" t="n">
-        <v>74.313954</v>
+        <v>73.55180799999999</v>
       </c>
       <c r="G173" t="n">
-        <v>110.486004</v>
+        <v>108.697587</v>
       </c>
       <c r="H173" t="n">
-        <v>162.224928</v>
+        <v>158.316989</v>
       </c>
       <c r="I173" t="n">
-        <v>269.753902</v>
+        <v>260.58498</v>
       </c>
       <c r="J173" t="n">
         <v>1167.6726</v>
@@ -13598,19 +13598,19 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>122290.076025</v>
+        <v>122311.923752</v>
       </c>
       <c r="F174" t="n">
-        <v>134848.057141</v>
+        <v>134901.686313</v>
       </c>
       <c r="G174" t="n">
-        <v>145924.141182</v>
+        <v>146025.480852</v>
       </c>
       <c r="H174" t="n">
-        <v>156392.911205</v>
+        <v>156585.174733</v>
       </c>
       <c r="I174" t="n">
-        <v>164565.600102</v>
+        <v>164986.908264</v>
       </c>
       <c r="J174" t="n">
         <v>140904.973626</v>
@@ -13674,19 +13674,19 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>278.712367</v>
+        <v>278.444907</v>
       </c>
       <c r="F175" t="n">
-        <v>473.124697</v>
+        <v>472.315583</v>
       </c>
       <c r="G175" t="n">
-        <v>754.937577</v>
+        <v>753.063624</v>
       </c>
       <c r="H175" t="n">
-        <v>1101.958812</v>
+        <v>1097.900477</v>
       </c>
       <c r="I175" t="n">
-        <v>1548.43706</v>
+        <v>1539.081012</v>
       </c>
       <c r="J175" t="n">
         <v>2830.979818</v>
@@ -13750,19 +13750,19 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>19.224676</v>
+        <v>19.145257</v>
       </c>
       <c r="F176" t="n">
-        <v>21.693305</v>
+        <v>21.491998</v>
       </c>
       <c r="G176" t="n">
-        <v>26.037756</v>
+        <v>25.628789</v>
       </c>
       <c r="H176" t="n">
-        <v>33.952417</v>
+        <v>33.140413</v>
       </c>
       <c r="I176" t="n">
-        <v>52.588638</v>
+        <v>50.810362</v>
       </c>
       <c r="J176" t="n">
         <v>214.344898</v>
@@ -13826,19 +13826,19 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>75143.16755500001</v>
+        <v>75139.273315</v>
       </c>
       <c r="F177" t="n">
-        <v>113930.006543</v>
+        <v>113939.886007</v>
       </c>
       <c r="G177" t="n">
-        <v>157413.344525</v>
+        <v>157477.041786</v>
       </c>
       <c r="H177" t="n">
-        <v>192109.302997</v>
+        <v>192292.507523</v>
       </c>
       <c r="I177" t="n">
-        <v>211880.188331</v>
+        <v>212332.11559</v>
       </c>
       <c r="J177" t="n">
         <v>188565.705831</v>
@@ -13902,19 +13902,19 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>24.158296</v>
+        <v>23.953848</v>
       </c>
       <c r="F178" t="n">
-        <v>35.971293</v>
+        <v>35.371822</v>
       </c>
       <c r="G178" t="n">
-        <v>53.252063</v>
+        <v>51.895784</v>
       </c>
       <c r="H178" t="n">
-        <v>82.940067</v>
+        <v>80.02506700000001</v>
       </c>
       <c r="I178" t="n">
-        <v>154.175045</v>
+        <v>147.396947</v>
       </c>
       <c r="J178" t="n">
         <v>807.459554</v>
@@ -13978,19 +13978,19 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>45.928411</v>
+        <v>45.809276</v>
       </c>
       <c r="F179" t="n">
-        <v>54.976033</v>
+        <v>54.662674</v>
       </c>
       <c r="G179" t="n">
-        <v>67.69206800000001</v>
+        <v>67.037222</v>
       </c>
       <c r="H179" t="n">
-        <v>85.117907</v>
+        <v>83.806984</v>
       </c>
       <c r="I179" t="n">
-        <v>118.645851</v>
+        <v>115.790369</v>
       </c>
       <c r="J179" t="n">
         <v>380.349646</v>
@@ -14130,55 +14130,55 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>0</v>
+        <v>1e-06</v>
       </c>
       <c r="F181" t="n">
+        <v>5e-06</v>
+      </c>
+      <c r="G181" t="n">
+        <v>-2e-06</v>
+      </c>
+      <c r="H181" t="n">
+        <v>-2e-06</v>
+      </c>
+      <c r="I181" t="n">
+        <v>-2e-06</v>
+      </c>
+      <c r="J181" t="n">
         <v>1e-06</v>
       </c>
-      <c r="G181" t="n">
+      <c r="K181" t="n">
+        <v>-3e-06</v>
+      </c>
+      <c r="L181" t="n">
+        <v>3e-06</v>
+      </c>
+      <c r="M181" t="n">
+        <v>2e-06</v>
+      </c>
+      <c r="N181" t="n">
+        <v>-4e-06</v>
+      </c>
+      <c r="O181" t="n">
+        <v>5e-06</v>
+      </c>
+      <c r="P181" t="n">
+        <v>2e-06</v>
+      </c>
+      <c r="Q181" t="n">
+        <v>4e-06</v>
+      </c>
+      <c r="R181" t="n">
         <v>-1e-06</v>
       </c>
-      <c r="H181" t="n">
+      <c r="S181" t="n">
+        <v>-4e-06</v>
+      </c>
+      <c r="T181" t="n">
         <v>4e-06</v>
       </c>
-      <c r="I181" t="n">
-        <v>-8e-06</v>
-      </c>
-      <c r="J181" t="n">
-        <v>-1e-06</v>
-      </c>
-      <c r="K181" t="n">
-        <v>-1e-06</v>
-      </c>
-      <c r="L181" t="n">
-        <v>0</v>
-      </c>
-      <c r="M181" t="n">
-        <v>7e-06</v>
-      </c>
-      <c r="N181" t="n">
-        <v>-1e-06</v>
-      </c>
-      <c r="O181" t="n">
-        <v>7e-06</v>
-      </c>
-      <c r="P181" t="n">
-        <v>-1e-06</v>
-      </c>
-      <c r="Q181" t="n">
-        <v>-2e-06</v>
-      </c>
-      <c r="R181" t="n">
-        <v>-5e-06</v>
-      </c>
-      <c r="S181" t="n">
+      <c r="U181" t="n">
         <v>-7e-06</v>
-      </c>
-      <c r="T181" t="n">
-        <v>0</v>
-      </c>
-      <c r="U181" t="n">
-        <v>-2e-06</v>
       </c>
       <c r="V181" t="n">
         <v>-6e-06</v>
